--- a/שבצק_יציאות_מסודר.xlsx
+++ b/שבצק_יציאות_מסודר.xlsx
@@ -2356,19 +2356,19 @@
       <c r="DA5" s="7" t="n"/>
       <c r="DB5" s="9">
         <f>COUNTIF(D5:DA5,"בסיס")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="DC5" s="9">
         <f>COUNTIF(D5:DA5,"בית")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="DD5" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D5:DA5="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE5" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D5:DA5="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2591,19 +2591,19 @@
       <c r="DA6" s="7" t="n"/>
       <c r="DB6" s="9">
         <f>COUNTIF(D6:DA6,"בסיס")</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="DC6" s="9">
         <f>COUNTIF(D6:DA6,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD6" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D6:DA6="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE6" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D6:DA6="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2854,19 +2854,19 @@
       <c r="DA7" s="7" t="n"/>
       <c r="DB7" s="9">
         <f>COUNTIF(D7:DA7,"בסיס")</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="DC7" s="9">
         <f>COUNTIF(D7:DA7,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD7" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D7:DA7="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE7" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D7:DA7="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3105,19 +3105,19 @@
       <c r="DA8" s="7" t="n"/>
       <c r="DB8" s="9">
         <f>COUNTIF(D8:DA8,"בסיס")</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="DC8" s="9">
         <f>COUNTIF(D8:DA8,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD8" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D8:DA8="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE8" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D8:DA8="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3420,19 +3420,19 @@
       <c r="DA9" s="7" t="n"/>
       <c r="DB9" s="9">
         <f>COUNTIF(D9:DA9,"בסיס")</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="DC9" s="9">
         <f>COUNTIF(D9:DA9,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD9" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D9:DA9="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE9" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D9:DA9="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3579,19 +3579,19 @@
       <c r="DA10" s="7" t="n"/>
       <c r="DB10" s="9">
         <f>COUNTIF(D10:DA10,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="DC10" s="9">
         <f>COUNTIF(D10:DA10,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD10" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D10:DA10="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE10" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D10:DA10="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3738,19 +3738,19 @@
       <c r="DA11" s="7" t="n"/>
       <c r="DB11" s="9">
         <f>COUNTIF(D11:DA11,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="DC11" s="9">
         <f>COUNTIF(D11:DA11,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD11" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D11:DA11="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE11" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D11:DA11="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3897,19 +3897,19 @@
       <c r="DA12" s="7" t="n"/>
       <c r="DB12" s="9">
         <f>COUNTIF(D12:DA12,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="DC12" s="9">
         <f>COUNTIF(D12:DA12,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD12" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D12:DA12="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE12" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D12:DA12="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4224,19 +4224,19 @@
       <c r="DA13" s="7" t="n"/>
       <c r="DB13" s="9">
         <f>COUNTIF(D13:DA13,"בסיס")</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="DC13" s="9">
         <f>COUNTIF(D13:DA13,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD13" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D13:DA13="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE13" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D13:DA13="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4555,19 +4555,19 @@
       <c r="DA14" s="7" t="n"/>
       <c r="DB14" s="9">
         <f>COUNTIF(D14:DA14,"בסיס")</f>
-        <v/>
+        <v>32</v>
       </c>
       <c r="DC14" s="9">
         <f>COUNTIF(D14:DA14,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD14" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D14:DA14="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE14" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D14:DA14="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4714,19 +4714,19 @@
       <c r="DA15" s="7" t="n"/>
       <c r="DB15" s="9">
         <f>COUNTIF(D15:DA15,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="DC15" s="9">
         <f>COUNTIF(D15:DA15,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD15" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D15:DA15="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE15" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D15:DA15="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4873,19 +4873,19 @@
       <c r="DA16" s="7" t="n"/>
       <c r="DB16" s="9">
         <f>COUNTIF(D16:DA16,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="DC16" s="9">
         <f>COUNTIF(D16:DA16,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD16" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D16:DA16="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE16" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D16:DA16="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5164,19 +5164,19 @@
       <c r="DA17" s="7" t="n"/>
       <c r="DB17" s="9">
         <f>COUNTIF(D17:DA17,"בסיס")</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="DC17" s="9">
         <f>COUNTIF(D17:DA17,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD17" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D17:DA17="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE17" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D17:DA17="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
       <c r="DA18" s="7" t="n"/>
       <c r="DB18" s="9">
         <f>COUNTIF(D18:DA18,"בסיס")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="DC18" s="9">
         <f>COUNTIF(D18:DA18,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD18" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D18:DA18="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE18" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D18:DA18="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5678,19 +5678,19 @@
       <c r="DA19" s="7" t="n"/>
       <c r="DB19" s="9">
         <f>COUNTIF(D19:DA19,"בסיס")</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="DC19" s="9">
         <f>COUNTIF(D19:DA19,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD19" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D19:DA19="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE19" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D19:DA19="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5985,19 +5985,19 @@
       <c r="DA20" s="7" t="n"/>
       <c r="DB20" s="9">
         <f>COUNTIF(D20:DA20,"בסיס")</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="DC20" s="9">
         <f>COUNTIF(D20:DA20,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD20" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D20:DA20="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE20" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D20:DA20="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -6260,19 +6260,19 @@
       <c r="DA21" s="7" t="n"/>
       <c r="DB21" s="9">
         <f>COUNTIF(D21:DA21,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="DC21" s="9">
         <f>COUNTIF(D21:DA21,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD21" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D21:DA21="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE21" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D21:DA21="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -6415,19 +6415,19 @@
       <c r="DA22" s="7" t="n"/>
       <c r="DB22" s="9">
         <f>COUNTIF(D22:DA22,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="DC22" s="9">
         <f>COUNTIF(D22:DA22,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD22" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D22:DA22="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE22" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D22:DA22="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -6594,19 +6594,19 @@
       <c r="DA23" s="7" t="n"/>
       <c r="DB23" s="9">
         <f>COUNTIF(D23:DA23,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="DC23" s="9">
         <f>COUNTIF(D23:DA23,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD23" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D23:DA23="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE23" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D23:DA23="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -6769,19 +6769,19 @@
       <c r="DA24" s="7" t="n"/>
       <c r="DB24" s="9">
         <f>COUNTIF(D24:DA24,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="DC24" s="9">
         <f>COUNTIF(D24:DA24,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD24" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D24:DA24="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE24" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D24:DA24="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -7196,19 +7196,19 @@
       <c r="DA25" s="7" t="n"/>
       <c r="DB25" s="9">
         <f>COUNTIF(D25:DA25,"בסיס")</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="DC25" s="9">
         <f>COUNTIF(D25:DA25,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD25" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D25:DA25="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE25" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D25:DA25="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -7483,19 +7483,19 @@
       <c r="DA26" s="7" t="n"/>
       <c r="DB26" s="9">
         <f>COUNTIF(D26:DA26,"בסיס")</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="DC26" s="9">
         <f>COUNTIF(D26:DA26,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD26" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D26:DA26="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE26" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D26:DA26="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -7642,19 +7642,19 @@
       <c r="DA27" s="7" t="n"/>
       <c r="DB27" s="9">
         <f>COUNTIF(D27:DA27,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="DC27" s="9">
         <f>COUNTIF(D27:DA27,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD27" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D27:DA27="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE27" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D27:DA27="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -8069,19 +8069,19 @@
       <c r="DA28" s="7" t="n"/>
       <c r="DB28" s="9">
         <f>COUNTIF(D28:DA28,"בסיס")</f>
-        <v/>
+        <v>38</v>
       </c>
       <c r="DC28" s="9">
         <f>COUNTIF(D28:DA28,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD28" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D28:DA28="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE28" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D28:DA28="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -8392,19 +8392,19 @@
       <c r="DA29" s="7" t="n"/>
       <c r="DB29" s="9">
         <f>COUNTIF(D29:DA29,"בסיס")</f>
-        <v/>
+        <v>29</v>
       </c>
       <c r="DC29" s="9">
         <f>COUNTIF(D29:DA29,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD29" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D29:DA29="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE29" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D29:DA29="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -8515,19 +8515,19 @@
       <c r="DA30" s="7" t="n"/>
       <c r="DB30" s="9">
         <f>COUNTIF(D30:DA30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DC30" s="9">
         <f>COUNTIF(D30:DA30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DD30" s="9">
         <f>SUMPRODUCT($D$36:$DA$36,--(D30:DA30="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DE30" s="9">
         <f>SUMPRODUCT($D$37:$DA$37,--(D30:DA30="בית"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="31" ht="19.95" customHeight="1" s="30">
@@ -8538,411 +8538,411 @@
       </c>
       <c r="D31" s="10">
         <f>COUNTIF(D5:D30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E31" s="10">
         <f>COUNTIF(E5:E30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F31" s="10">
         <f>COUNTIF(F5:F30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G31" s="10">
         <f>COUNTIF(G5:G30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H31" s="10">
         <f>COUNTIF(H5:H30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I31" s="10">
         <f>COUNTIF(I5:I30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J31" s="10">
         <f>COUNTIF(J5:J30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K31" s="10">
         <f>COUNTIF(K5:K30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L31" s="10">
         <f>COUNTIF(L5:L30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M31" s="10">
         <f>COUNTIF(M5:M30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N31" s="10">
         <f>COUNTIF(N5:N30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="O31" s="10">
         <f>COUNTIF(O5:O30,"בסיס")</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="P31" s="10">
         <f>COUNTIF(P5:P30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q31" s="10">
         <f>COUNTIF(Q5:Q30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R31" s="10">
         <f>COUNTIF(R5:R30,"בסיס")</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="S31" s="10">
         <f>COUNTIF(S5:S30,"בסיס")</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="T31" s="10">
         <f>COUNTIF(T5:T30,"בסיס")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="U31" s="10">
         <f>COUNTIF(U5:U30,"בסיס")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="V31" s="10">
         <f>COUNTIF(V5:V30,"בסיס")</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="W31" s="10">
         <f>COUNTIF(W5:W30,"בסיס")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="X31" s="10">
         <f>COUNTIF(X5:X30,"בסיס")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="Y31" s="10">
         <f>COUNTIF(Y5:Y30,"בסיס")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="Z31" s="10">
         <f>COUNTIF(Z5:Z30,"בסיס")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AA31" s="10">
         <f>COUNTIF(AA5:AA30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AB31" s="10">
         <f>COUNTIF(AB5:AB30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC31" s="10">
         <f>COUNTIF(AC5:AC30,"בסיס")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AD31" s="10">
         <f>COUNTIF(AD5:AD30,"בסיס")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE31" s="10">
         <f>COUNTIF(AE5:AE30,"בסיס")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AF31" s="10">
         <f>COUNTIF(AF5:AF30,"בסיס")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG31" s="10">
         <f>COUNTIF(AG5:AG30,"בסיס")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AH31" s="10">
         <f>COUNTIF(AH5:AH30,"בסיס")</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="AI31" s="10">
         <f>COUNTIF(AI5:AI30,"בסיס")</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="AJ31" s="10">
         <f>COUNTIF(AJ5:AJ30,"בסיס")</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="AK31" s="10">
         <f>COUNTIF(AK5:AK30,"בסיס")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AL31" s="10">
         <f>COUNTIF(AL5:AL30,"בסיס")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AM31" s="10">
         <f>COUNTIF(AM5:AM30,"בסיס")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AN31" s="10">
         <f>COUNTIF(AN5:AN30,"בסיס")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO31" s="10">
         <f>COUNTIF(AO5:AO30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AP31" s="10">
         <f>COUNTIF(AP5:AP30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AQ31" s="10">
         <f>COUNTIF(AQ5:AQ30,"בסיס")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AR31" s="10">
         <f>COUNTIF(AR5:AR30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AS31" s="10">
         <f>COUNTIF(AS5:AS30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AT31" s="10">
         <f>COUNTIF(AT5:AT30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AU31" s="10">
         <f>COUNTIF(AU5:AU30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AV31" s="10">
         <f>COUNTIF(AV5:AV30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AW31" s="10">
         <f>COUNTIF(AW5:AW30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AX31" s="10">
         <f>COUNTIF(AX5:AX30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AY31" s="10">
         <f>COUNTIF(AY5:AY30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AZ31" s="10">
         <f>COUNTIF(AZ5:AZ30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="BA31" s="10">
         <f>COUNTIF(BA5:BA30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="BB31" s="10">
         <f>COUNTIF(BB5:BB30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BC31" s="10">
         <f>COUNTIF(BC5:BC30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BD31" s="10">
         <f>COUNTIF(BD5:BD30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BE31" s="10">
         <f>COUNTIF(BE5:BE30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="BF31" s="10">
         <f>COUNTIF(BF5:BF30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BG31" s="10">
         <f>COUNTIF(BG5:BG30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BH31" s="10">
         <f>COUNTIF(BH5:BH30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="BI31" s="10">
         <f>COUNTIF(BI5:BI30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BJ31" s="10">
         <f>COUNTIF(BJ5:BJ30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BK31" s="10">
         <f>COUNTIF(BK5:BK30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BL31" s="10">
         <f>COUNTIF(BL5:BL30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BM31" s="10">
         <f>COUNTIF(BM5:BM30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BN31" s="10">
         <f>COUNTIF(BN5:BN30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BO31" s="10">
         <f>COUNTIF(BO5:BO30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BP31" s="10">
         <f>COUNTIF(BP5:BP30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ31" s="10">
         <f>COUNTIF(BQ5:BQ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BR31" s="10">
         <f>COUNTIF(BR5:BR30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BS31" s="10">
         <f>COUNTIF(BS5:BS30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BT31" s="10">
         <f>COUNTIF(BT5:BT30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BU31" s="10">
         <f>COUNTIF(BU5:BU30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BV31" s="10">
         <f>COUNTIF(BV5:BV30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BW31" s="10">
         <f>COUNTIF(BW5:BW30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BX31" s="10">
         <f>COUNTIF(BX5:BX30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BY31" s="10">
         <f>COUNTIF(BY5:BY30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BZ31" s="10">
         <f>COUNTIF(BZ5:BZ30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="CA31" s="10">
         <f>COUNTIF(CA5:CA30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CB31" s="10">
         <f>COUNTIF(CB5:CB30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CC31" s="10">
         <f>COUNTIF(CC5:CC30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CD31" s="10">
         <f>COUNTIF(CD5:CD30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE31" s="10">
         <f>COUNTIF(CE5:CE30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CF31" s="10">
         <f>COUNTIF(CF5:CF30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CG31" s="10">
         <f>COUNTIF(CG5:CG30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CH31" s="10">
         <f>COUNTIF(CH5:CH30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CI31" s="10">
         <f>COUNTIF(CI5:CI30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CJ31" s="10">
         <f>COUNTIF(CJ5:CJ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK31" s="10">
         <f>COUNTIF(CK5:CK30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CL31" s="10">
         <f>COUNTIF(CL5:CL30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CM31" s="10">
         <f>COUNTIF(CM5:CM30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CN31" s="10">
         <f>COUNTIF(CN5:CN30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CO31" s="10">
         <f>COUNTIF(CO5:CO30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CP31" s="10">
         <f>COUNTIF(CP5:CP30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CQ31" s="10">
         <f>COUNTIF(CQ5:CQ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CR31" s="10">
         <f>COUNTIF(CR5:CR30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CS31" s="10">
         <f>COUNTIF(CS5:CS30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CT31" s="10">
         <f>COUNTIF(CT5:CT30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CU31" s="10">
         <f>COUNTIF(CU5:CU30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CV31" s="10">
         <f>COUNTIF(CV5:CV30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CW31" s="10">
         <f>COUNTIF(CW5:CW30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CX31" s="10">
         <f>COUNTIF(CX5:CX30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CY31" s="10">
         <f>COUNTIF(CY5:CY30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CZ31" s="10">
         <f>COUNTIF(CZ5:CZ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DA31" s="10">
         <f>COUNTIF(DA5:DA30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -8953,411 +8953,411 @@
       </c>
       <c r="D32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",D5:D30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",E5:E30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",F5:F30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",G5:G30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",H5:H30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",I5:I30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",J5:J30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",K5:K30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",L5:L30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",M5:M30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",N5:N30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",O5:O30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",P5:P30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",Q5:Q30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",R5:R30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="S32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",S5:S30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="T32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",T5:T30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="U32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",U5:U30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="V32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",V5:V30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",W5:W30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="X32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",X5:X30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",Y5:Y30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Z32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",Z5:Z30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AA5:AA30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AB32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AB5:AB30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AC5:AC30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AD32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AD5:AD30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AE5:AE30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AF32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AF5:AF30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AG32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AG5:AG30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AH32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AH5:AH30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AI32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AI5:AI30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AJ32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AJ5:AJ30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AK32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AK5:AK30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AL32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AL5:AL30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AM32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AM5:AM30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AN32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AN5:AN30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AO5:AO30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AP32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AP5:AP30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AQ32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AQ5:AQ30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AR32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AR5:AR30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AS32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AS5:AS30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AT32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AT5:AT30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AU32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AU5:AU30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AV32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AV5:AV30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AW32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AW5:AW30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AX32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AX5:AX30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AY32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AY5:AY30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AZ32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",AZ5:AZ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BA32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BA5:BA30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BB5:BB30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BC5:BC30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BD5:BD30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BE32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BE5:BE30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BF32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BF5:BF30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BG32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BG5:BG30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BH5:BH30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BI32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BI5:BI30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BJ32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BJ5:BJ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BK5:BK30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BL5:BL30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BM32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BM5:BM30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BN32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BN5:BN30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BO32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BO5:BO30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BP32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BP5:BP30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BQ5:BQ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BR32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BR5:BR30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BS32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BS5:BS30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BT32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BT5:BT30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BU32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BU5:BU30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BV32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BV5:BV30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BW32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BW5:BW30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BX5:BX30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BY32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BY5:BY30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BZ32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",BZ5:BZ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CA32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CA5:CA30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CB32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CB5:CB30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CC32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CC5:CC30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CD32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CD5:CD30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CE5:CE30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CF32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CF5:CF30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CG32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CG5:CG30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CH32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CH5:CH30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CI32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CI5:CI30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CJ32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CJ5:CJ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CK5:CK30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CL32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CL5:CL30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CM32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CM5:CM30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CN32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CN5:CN30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CO32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CO5:CO30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CP32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CP5:CP30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CQ32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CQ5:CQ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CR32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CR5:CR30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CS32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CS5:CS30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CT32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CT5:CT30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CU32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CU5:CU30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CV32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CV5:CV30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CW32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CW5:CW30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CX32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CX5:CX30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CY32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CY5:CY30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CZ32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",CZ5:CZ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DA32" s="10">
         <f>COUNTIFS($B$5:$B$30,"*מחתים*",DA5:DA30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -9368,411 +9368,411 @@
       </c>
       <c r="D33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",D5:D30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",E5:E30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",F5:F30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",G5:G30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",H5:H30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",I5:I30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",J5:J30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",K5:K30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",L5:L30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",M5:M30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",N5:N30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",O5:O30,"בסיס")</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="P33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",P5:P30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",Q5:Q30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",R5:R30,"בסיס")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="S33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",S5:S30,"בסיס")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="T33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",T5:T30,"בסיס")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="U33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",U5:U30,"בסיס")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="V33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",V5:V30,"בסיס")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="W33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",W5:W30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="X33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",X5:X30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Y33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",Y5:Y30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="Z33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",Z5:Z30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AA5:AA30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AB33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AB5:AB30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AC33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AC5:AC30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AD33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AD5:AD30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AE33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AE5:AE30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AF33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AF5:AF30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AG33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AG5:AG30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AH33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AH5:AH30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AI33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AI5:AI30,"בסיס")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AJ5:AJ30,"בסיס")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AK33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AK5:AK30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AL33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AL5:AL30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AM33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AM5:AM30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AN33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AN5:AN30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AO5:AO30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AP33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AP5:AP30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AQ33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AQ5:AQ30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AR33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AR5:AR30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AS33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AS5:AS30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AT33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AT5:AT30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AU33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AU5:AU30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AV33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AV5:AV30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AW33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AW5:AW30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AX33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AX5:AX30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AY33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AY5:AY30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AZ33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",AZ5:AZ30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="BA33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BA5:BA30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="BB33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BB5:BB30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BC33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BC5:BC30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BD33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BD5:BD30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BE33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BE5:BE30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="BF33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BF5:BF30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BG33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BG5:BG30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BH33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BH5:BH30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="BI33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BI5:BI30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BJ33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BJ5:BJ30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BK33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BK5:BK30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BL33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BL5:BL30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BM33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BM5:BM30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BN33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BN5:BN30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BO33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BO5:BO30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BP33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BP5:BP30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BQ5:BQ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BR33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BR5:BR30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BS33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BS5:BS30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BT33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BT5:BT30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BU33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BU5:BU30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BV33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BV5:BV30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BW33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BW5:BW30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BX33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BX5:BX30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BY33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BY5:BY30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BZ33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",BZ5:BZ30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="CA33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CA5:CA30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CB33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CB5:CB30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CC33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CC5:CC30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CD33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CD5:CD30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CE5:CE30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CF33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CF5:CF30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CG33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CG5:CG30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CH33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CH5:CH30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CI33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CI5:CI30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CJ33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CJ5:CJ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CK5:CK30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CL33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CL5:CL30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CM33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CM5:CM30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CN33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CN5:CN30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CO33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CO5:CO30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CP33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CP5:CP30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CQ33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CQ5:CQ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CR33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CR5:CR30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CS33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CS5:CS30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CT33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CT5:CT30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CU33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CU5:CU30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CV33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CV5:CV30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CW33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CW5:CW30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CX33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CX5:CX30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CY33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CY5:CY30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CZ33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",CZ5:CZ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DA33" s="10">
         <f>COUNTIFS($B$5:$B$30,"*לוגיסטיקה*",DA5:DA30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -9783,411 +9783,411 @@
       </c>
       <c r="D34" s="10">
         <f>COUNTIF(D5:D30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E34" s="10">
         <f>COUNTIF(E5:E30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F34" s="10">
         <f>COUNTIF(F5:F30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G34" s="10">
         <f>COUNTIF(G5:G30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H34" s="10">
         <f>COUNTIF(H5:H30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I34" s="10">
         <f>COUNTIF(I5:I30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J34" s="10">
         <f>COUNTIF(J5:J30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K34" s="10">
         <f>COUNTIF(K5:K30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L34" s="10">
         <f>COUNTIF(L5:L30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M34" s="10">
         <f>COUNTIF(M5:M30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N34" s="10">
         <f>COUNTIF(N5:N30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O34" s="10">
         <f>COUNTIF(O5:O30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P34" s="10">
         <f>COUNTIF(P5:P30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q34" s="10">
         <f>COUNTIF(Q5:Q30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R34" s="10">
         <f>COUNTIF(R5:R30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S34" s="10">
         <f>COUNTIF(S5:S30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T34" s="10">
         <f>COUNTIF(T5:T30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U34" s="10">
         <f>COUNTIF(U5:U30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V34" s="10">
         <f>COUNTIF(V5:V30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W34" s="10">
         <f>COUNTIF(W5:W30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X34" s="10">
         <f>COUNTIF(X5:X30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y34" s="10">
         <f>COUNTIF(Y5:Y30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Z34" s="10">
         <f>COUNTIF(Z5:Z30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA34" s="10">
         <f>COUNTIF(AA5:AA30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AB34" s="10">
         <f>COUNTIF(AB5:AB30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC34" s="10">
         <f>COUNTIF(AC5:AC30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD34" s="10">
         <f>COUNTIF(AD5:AD30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE34" s="10">
         <f>COUNTIF(AE5:AE30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF34" s="10">
         <f>COUNTIF(AF5:AF30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG34" s="10">
         <f>COUNTIF(AG5:AG30,"בית")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AH34" s="10">
         <f>COUNTIF(AH5:AH30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI34" s="10">
         <f>COUNTIF(AI5:AI30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ34" s="10">
         <f>COUNTIF(AJ5:AJ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK34" s="10">
         <f>COUNTIF(AK5:AK30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL34" s="10">
         <f>COUNTIF(AL5:AL30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM34" s="10">
         <f>COUNTIF(AM5:AM30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AN34" s="10">
         <f>COUNTIF(AN5:AN30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO34" s="10">
         <f>COUNTIF(AO5:AO30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AP34" s="10">
         <f>COUNTIF(AP5:AP30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ34" s="10">
         <f>COUNTIF(AQ5:AQ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AR34" s="10">
         <f>COUNTIF(AR5:AR30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS34" s="10">
         <f>COUNTIF(AS5:AS30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT34" s="10">
         <f>COUNTIF(AT5:AT30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU34" s="10">
         <f>COUNTIF(AU5:AU30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AV34" s="10">
         <f>COUNTIF(AV5:AV30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AW34" s="10">
         <f>COUNTIF(AW5:AW30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AX34" s="10">
         <f>COUNTIF(AX5:AX30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AY34" s="10">
         <f>COUNTIF(AY5:AY30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AZ34" s="10">
         <f>COUNTIF(AZ5:AZ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BA34" s="10">
         <f>COUNTIF(BA5:BA30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB34" s="10">
         <f>COUNTIF(BB5:BB30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC34" s="10">
         <f>COUNTIF(BC5:BC30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD34" s="10">
         <f>COUNTIF(BD5:BD30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BE34" s="10">
         <f>COUNTIF(BE5:BE30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BF34" s="10">
         <f>COUNTIF(BF5:BF30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BG34" s="10">
         <f>COUNTIF(BG5:BG30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH34" s="10">
         <f>COUNTIF(BH5:BH30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BI34" s="10">
         <f>COUNTIF(BI5:BI30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BJ34" s="10">
         <f>COUNTIF(BJ5:BJ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK34" s="10">
         <f>COUNTIF(BK5:BK30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL34" s="10">
         <f>COUNTIF(BL5:BL30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BM34" s="10">
         <f>COUNTIF(BM5:BM30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BN34" s="10">
         <f>COUNTIF(BN5:BN30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BO34" s="10">
         <f>COUNTIF(BO5:BO30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BP34" s="10">
         <f>COUNTIF(BP5:BP30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ34" s="10">
         <f>COUNTIF(BQ5:BQ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BR34" s="10">
         <f>COUNTIF(BR5:BR30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BS34" s="10">
         <f>COUNTIF(BS5:BS30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BT34" s="10">
         <f>COUNTIF(BT5:BT30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BU34" s="10">
         <f>COUNTIF(BU5:BU30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BV34" s="10">
         <f>COUNTIF(BV5:BV30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BW34" s="10">
         <f>COUNTIF(BW5:BW30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX34" s="10">
         <f>COUNTIF(BX5:BX30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BY34" s="10">
         <f>COUNTIF(BY5:BY30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BZ34" s="10">
         <f>COUNTIF(BZ5:BZ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CA34" s="10">
         <f>COUNTIF(CA5:CA30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CB34" s="10">
         <f>COUNTIF(CB5:CB30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CC34" s="10">
         <f>COUNTIF(CC5:CC30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CD34" s="10">
         <f>COUNTIF(CD5:CD30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE34" s="10">
         <f>COUNTIF(CE5:CE30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CF34" s="10">
         <f>COUNTIF(CF5:CF30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CG34" s="10">
         <f>COUNTIF(CG5:CG30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CH34" s="10">
         <f>COUNTIF(CH5:CH30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CI34" s="10">
         <f>COUNTIF(CI5:CI30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CJ34" s="10">
         <f>COUNTIF(CJ5:CJ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK34" s="10">
         <f>COUNTIF(CK5:CK30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CL34" s="10">
         <f>COUNTIF(CL5:CL30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CM34" s="10">
         <f>COUNTIF(CM5:CM30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CN34" s="10">
         <f>COUNTIF(CN5:CN30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CO34" s="10">
         <f>COUNTIF(CO5:CO30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CP34" s="10">
         <f>COUNTIF(CP5:CP30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CQ34" s="10">
         <f>COUNTIF(CQ5:CQ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CR34" s="10">
         <f>COUNTIF(CR5:CR30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CS34" s="10">
         <f>COUNTIF(CS5:CS30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CT34" s="10">
         <f>COUNTIF(CT5:CT30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CU34" s="10">
         <f>COUNTIF(CU5:CU30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CV34" s="10">
         <f>COUNTIF(CV5:CV30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CW34" s="10">
         <f>COUNTIF(CW5:CW30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CX34" s="10">
         <f>COUNTIF(CX5:CX30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CY34" s="10">
         <f>COUNTIF(CY5:CY30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CZ34" s="10">
         <f>COUNTIF(CZ5:CZ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DA34" s="10">
         <f>COUNTIF(DA5:DA30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -10198,411 +10198,411 @@
       </c>
       <c r="D35" s="10">
         <f>COUNTA(D5:D30)-COUNTIF(D5:D30,"בסיס")</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="E35" s="10">
         <f>COUNTA(E5:E30)-COUNTIF(E5:E30,"בסיס")</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="F35" s="10">
         <f>COUNTA(F5:F30)-COUNTIF(F5:F30,"בסיס")</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="G35" s="10">
         <f>COUNTA(G5:G30)-COUNTIF(G5:G30,"בסיס")</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="H35" s="10">
         <f>COUNTA(H5:H30)-COUNTIF(H5:H30,"בסיס")</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="I35" s="10">
         <f>COUNTA(I5:I30)-COUNTIF(I5:I30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J35" s="10">
         <f>COUNTA(J5:J30)-COUNTIF(J5:J30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="K35" s="10">
         <f>COUNTA(K5:K30)-COUNTIF(K5:K30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L35" s="10">
         <f>COUNTA(L5:L30)-COUNTIF(L5:L30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M35" s="10">
         <f>COUNTA(M5:M30)-COUNTIF(M5:M30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N35" s="10">
         <f>COUNTA(N5:N30)-COUNTIF(N5:N30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O35" s="10">
         <f>COUNTA(O5:O30)-COUNTIF(O5:O30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P35" s="10">
         <f>COUNTA(P5:P30)-COUNTIF(P5:P30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q35" s="10">
         <f>COUNTA(Q5:Q30)-COUNTIF(Q5:Q30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R35" s="10">
         <f>COUNTA(R5:R30)-COUNTIF(R5:R30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="S35" s="10">
         <f>COUNTA(S5:S30)-COUNTIF(S5:S30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T35" s="10">
         <f>COUNTA(T5:T30)-COUNTIF(T5:T30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U35" s="10">
         <f>COUNTA(U5:U30)-COUNTIF(U5:U30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="V35" s="10">
         <f>COUNTA(V5:V30)-COUNTIF(V5:V30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="W35" s="10">
         <f>COUNTA(W5:W30)-COUNTIF(W5:W30,"בסיס")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="X35" s="10">
         <f>COUNTA(X5:X30)-COUNTIF(X5:X30,"בסיס")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="Y35" s="10">
         <f>COUNTA(Y5:Y30)-COUNTIF(Y5:Y30,"בסיס")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Z35" s="10">
         <f>COUNTA(Z5:Z30)-COUNTIF(Z5:Z30,"בסיס")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AA35" s="10">
         <f>COUNTA(AA5:AA30)-COUNTIF(AA5:AA30,"בסיס")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AB35" s="10">
         <f>COUNTA(AB5:AB30)-COUNTIF(AB5:AB30,"בסיס")</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="AC35" s="10">
         <f>COUNTA(AC5:AC30)-COUNTIF(AC5:AC30,"בסיס")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AD35" s="10">
         <f>COUNTA(AD5:AD30)-COUNTIF(AD5:AD30,"בסיס")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AE35" s="10">
         <f>COUNTA(AE5:AE30)-COUNTIF(AE5:AE30,"בסיס")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AF35" s="10">
         <f>COUNTA(AF5:AF30)-COUNTIF(AF5:AF30,"בסיס")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AG35" s="10">
         <f>COUNTA(AG5:AG30)-COUNTIF(AG5:AG30,"בסיס")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AH35" s="10">
         <f>COUNTA(AH5:AH30)-COUNTIF(AH5:AH30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI35" s="10">
         <f>COUNTA(AI5:AI30)-COUNTIF(AI5:AI30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AJ35" s="10">
         <f>COUNTA(AJ5:AJ30)-COUNTIF(AJ5:AJ30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AK35" s="10">
         <f>COUNTA(AK5:AK30)-COUNTIF(AK5:AK30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AL35" s="10">
         <f>COUNTA(AL5:AL30)-COUNTIF(AL5:AL30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AM35" s="10">
         <f>COUNTA(AM5:AM30)-COUNTIF(AM5:AM30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AN35" s="10">
         <f>COUNTA(AN5:AN30)-COUNTIF(AN5:AN30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AO35" s="10">
         <f>COUNTA(AO5:AO30)-COUNTIF(AO5:AO30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AP35" s="10">
         <f>COUNTA(AP5:AP30)-COUNTIF(AP5:AP30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AQ35" s="10">
         <f>COUNTA(AQ5:AQ30)-COUNTIF(AQ5:AQ30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AR35" s="10">
         <f>COUNTA(AR5:AR30)-COUNTIF(AR5:AR30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AS35" s="10">
         <f>COUNTA(AS5:AS30)-COUNTIF(AS5:AS30,"בסיס")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AT35" s="10">
         <f>COUNTA(AT5:AT30)-COUNTIF(AT5:AT30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AU35" s="10">
         <f>COUNTA(AU5:AU30)-COUNTIF(AU5:AU30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AV35" s="10">
         <f>COUNTA(AV5:AV30)-COUNTIF(AV5:AV30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AW35" s="10">
         <f>COUNTA(AW5:AW30)-COUNTIF(AW5:AW30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AX35" s="10">
         <f>COUNTA(AX5:AX30)-COUNTIF(AX5:AX30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AY35" s="10">
         <f>COUNTA(AY5:AY30)-COUNTIF(AY5:AY30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AZ35" s="10">
         <f>COUNTA(AZ5:AZ30)-COUNTIF(AZ5:AZ30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="BA35" s="10">
         <f>COUNTA(BA5:BA30)-COUNTIF(BA5:BA30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="BB35" s="10">
         <f>COUNTA(BB5:BB30)-COUNTIF(BB5:BB30,"בסיס")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="BC35" s="10">
         <f>COUNTA(BC5:BC30)-COUNTIF(BC5:BC30,"בסיס")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="BD35" s="10">
         <f>COUNTA(BD5:BD30)-COUNTIF(BD5:BD30,"בסיס")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="BE35" s="10">
         <f>COUNTA(BE5:BE30)-COUNTIF(BE5:BE30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BF35" s="10">
         <f>COUNTA(BF5:BF30)-COUNTIF(BF5:BF30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BG35" s="10">
         <f>COUNTA(BG5:BG30)-COUNTIF(BG5:BG30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BH35" s="10">
         <f>COUNTA(BH5:BH30)-COUNTIF(BH5:BH30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BI35" s="10">
         <f>COUNTA(BI5:BI30)-COUNTIF(BI5:BI30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BJ35" s="10">
         <f>COUNTA(BJ5:BJ30)-COUNTIF(BJ5:BJ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK35" s="10">
         <f>COUNTA(BK5:BK30)-COUNTIF(BK5:BK30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL35" s="10">
         <f>COUNTA(BL5:BL30)-COUNTIF(BL5:BL30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BM35" s="10">
         <f>COUNTA(BM5:BM30)-COUNTIF(BM5:BM30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BN35" s="10">
         <f>COUNTA(BN5:BN30)-COUNTIF(BN5:BN30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BO35" s="10">
         <f>COUNTA(BO5:BO30)-COUNTIF(BO5:BO30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BP35" s="10">
         <f>COUNTA(BP5:BP30)-COUNTIF(BP5:BP30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BQ35" s="10">
         <f>COUNTA(BQ5:BQ30)-COUNTIF(BQ5:BQ30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BR35" s="10">
         <f>COUNTA(BR5:BR30)-COUNTIF(BR5:BR30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BS35" s="10">
         <f>COUNTA(BS5:BS30)-COUNTIF(BS5:BS30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BT35" s="10">
         <f>COUNTA(BT5:BT30)-COUNTIF(BT5:BT30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BU35" s="10">
         <f>COUNTA(BU5:BU30)-COUNTIF(BU5:BU30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BV35" s="10">
         <f>COUNTA(BV5:BV30)-COUNTIF(BV5:BV30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BW35" s="10">
         <f>COUNTA(BW5:BW30)-COUNTIF(BW5:BW30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX35" s="10">
         <f>COUNTA(BX5:BX30)-COUNTIF(BX5:BX30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BY35" s="10">
         <f>COUNTA(BY5:BY30)-COUNTIF(BY5:BY30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BZ35" s="10">
         <f>COUNTA(BZ5:BZ30)-COUNTIF(BZ5:BZ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CA35" s="10">
         <f>COUNTA(CA5:CA30)-COUNTIF(CA5:CA30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CB35" s="10">
         <f>COUNTA(CB5:CB30)-COUNTIF(CB5:CB30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CC35" s="10">
         <f>COUNTA(CC5:CC30)-COUNTIF(CC5:CC30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CD35" s="10">
         <f>COUNTA(CD5:CD30)-COUNTIF(CD5:CD30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="CE35" s="10">
         <f>COUNTA(CE5:CE30)-COUNTIF(CE5:CE30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="CF35" s="10">
         <f>COUNTA(CF5:CF30)-COUNTIF(CF5:CF30,"בסיס")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="CG35" s="10">
         <f>COUNTA(CG5:CG30)-COUNTIF(CG5:CG30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CH35" s="10">
         <f>COUNTA(CH5:CH30)-COUNTIF(CH5:CH30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CI35" s="10">
         <f>COUNTA(CI5:CI30)-COUNTIF(CI5:CI30,"בסיס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CJ35" s="10">
         <f>COUNTA(CJ5:CJ30)-COUNTIF(CJ5:CJ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK35" s="10">
         <f>COUNTA(CK5:CK30)-COUNTIF(CK5:CK30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CL35" s="10">
         <f>COUNTA(CL5:CL30)-COUNTIF(CL5:CL30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CM35" s="10">
         <f>COUNTA(CM5:CM30)-COUNTIF(CM5:CM30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CN35" s="10">
         <f>COUNTA(CN5:CN30)-COUNTIF(CN5:CN30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CO35" s="10">
         <f>COUNTA(CO5:CO30)-COUNTIF(CO5:CO30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CP35" s="10">
         <f>COUNTA(CP5:CP30)-COUNTIF(CP5:CP30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CQ35" s="10">
         <f>COUNTA(CQ5:CQ30)-COUNTIF(CQ5:CQ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CR35" s="10">
         <f>COUNTA(CR5:CR30)-COUNTIF(CR5:CR30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CS35" s="10">
         <f>COUNTA(CS5:CS30)-COUNTIF(CS5:CS30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CT35" s="10">
         <f>COUNTA(CT5:CT30)-COUNTIF(CT5:CT30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CU35" s="10">
         <f>COUNTA(CU5:CU30)-COUNTIF(CU5:CU30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CV35" s="10">
         <f>COUNTA(CV5:CV30)-COUNTIF(CV5:CV30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CW35" s="10">
         <f>COUNTA(CW5:CW30)-COUNTIF(CW5:CW30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CX35" s="10">
         <f>COUNTA(CX5:CX30)-COUNTIF(CX5:CX30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CY35" s="10">
         <f>COUNTA(CY5:CY30)-COUNTIF(CY5:CY30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CZ35" s="10">
         <f>COUNTA(CZ5:CZ30)-COUNTIF(CZ5:CZ30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DA35" s="10">
         <f>COUNTA(DA5:DA30)-COUNTIF(DA5:DA30,"בסיס")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="36" hidden="1" s="30">
@@ -11265,411 +11265,411 @@
       </c>
       <c r="D44" s="39">
         <f>COUNTIF(D5:D30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E44" s="39">
         <f>COUNTIF(E5:E30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F44" s="39">
         <f>COUNTIF(F5:F30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G44" s="39">
         <f>COUNTIF(G5:G30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H44" s="39">
         <f>COUNTIF(H5:H30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I44" s="39">
         <f>COUNTIF(I5:I30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J44" s="39">
         <f>COUNTIF(J5:J30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K44" s="39">
         <f>COUNTIF(K5:K30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L44" s="39">
         <f>COUNTIF(L5:L30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M44" s="39">
         <f>COUNTIF(M5:M30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N44" s="39">
         <f>COUNTIF(N5:N30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O44" s="39">
         <f>COUNTIF(O5:O30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P44" s="39">
         <f>COUNTIF(P5:P30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q44" s="39">
         <f>COUNTIF(Q5:Q30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R44" s="39">
         <f>COUNTIF(R5:R30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S44" s="39">
         <f>COUNTIF(S5:S30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T44" s="39">
         <f>COUNTIF(T5:T30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U44" s="39">
         <f>COUNTIF(U5:U30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V44" s="39">
         <f>COUNTIF(V5:V30,"חופשה")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="W44" s="39">
         <f>COUNTIF(W5:W30,"חופשה")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="X44" s="39">
         <f>COUNTIF(X5:X30,"חופשה")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y44" s="39">
         <f>COUNTIF(Y5:Y30,"חופשה")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Z44" s="39">
         <f>COUNTIF(Z5:Z30,"חופשה")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA44" s="39">
         <f>COUNTIF(AA5:AA30,"חופשה")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AB44" s="39">
         <f>COUNTIF(AB5:AB30,"חופשה")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AC44" s="39">
         <f>COUNTIF(AC5:AC30,"חופשה")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AD44" s="39">
         <f>COUNTIF(AD5:AD30,"חופשה")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AE44" s="39">
         <f>COUNTIF(AE5:AE30,"חופשה")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AF44" s="39">
         <f>COUNTIF(AF5:AF30,"חופשה")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG44" s="39">
         <f>COUNTIF(AG5:AG30,"חופשה")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AH44" s="39">
         <f>COUNTIF(AH5:AH30,"חופשה")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AI44" s="39">
         <f>COUNTIF(AI5:AI30,"חופשה")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AJ44" s="39">
         <f>COUNTIF(AJ5:AJ30,"חופשה")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK44" s="39">
         <f>COUNTIF(AK5:AK30,"חופשה")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AL44" s="39">
         <f>COUNTIF(AL5:AL30,"חופשה")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AM44" s="39">
         <f>COUNTIF(AM5:AM30,"חופשה")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AN44" s="39">
         <f>COUNTIF(AN5:AN30,"חופשה")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO44" s="39">
         <f>COUNTIF(AO5:AO30,"חופשה")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AP44" s="39">
         <f>COUNTIF(AP5:AP30,"חופשה")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AQ44" s="39">
         <f>COUNTIF(AQ5:AQ30,"חופשה")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AR44" s="39">
         <f>COUNTIF(AR5:AR30,"חופשה")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AS44" s="39">
         <f>COUNTIF(AS5:AS30,"חופשה")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AT44" s="39">
         <f>COUNTIF(AT5:AT30,"חופשה")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AU44" s="39">
         <f>COUNTIF(AU5:AU30,"חופשה")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AV44" s="39">
         <f>COUNTIF(AV5:AV30,"חופשה")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AW44" s="39">
         <f>COUNTIF(AW5:AW30,"חופשה")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AX44" s="39">
         <f>COUNTIF(AX5:AX30,"חופשה")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AY44" s="39">
         <f>COUNTIF(AY5:AY30,"חופשה")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AZ44" s="39">
         <f>COUNTIF(AZ5:AZ30,"חופשה")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="BA44" s="39">
         <f>COUNTIF(BA5:BA30,"חופשה")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="BB44" s="39">
         <f>COUNTIF(BB5:BB30,"חופשה")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="BC44" s="39">
         <f>COUNTIF(BC5:BC30,"חופשה")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="BD44" s="39">
         <f>COUNTIF(BD5:BD30,"חופשה")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BE44" s="39">
         <f>COUNTIF(BE5:BE30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BF44" s="39">
         <f>COUNTIF(BF5:BF30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BG44" s="39">
         <f>COUNTIF(BG5:BG30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BH44" s="39">
         <f>COUNTIF(BH5:BH30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BI44" s="39">
         <f>COUNTIF(BI5:BI30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BJ44" s="39">
         <f>COUNTIF(BJ5:BJ30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK44" s="39">
         <f>COUNTIF(BK5:BK30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL44" s="39">
         <f>COUNTIF(BL5:BL30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BM44" s="39">
         <f>COUNTIF(BM5:BM30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BN44" s="39">
         <f>COUNTIF(BN5:BN30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BO44" s="39">
         <f>COUNTIF(BO5:BO30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BP44" s="39">
         <f>COUNTIF(BP5:BP30,"חופשה")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BQ44" s="39">
         <f>COUNTIF(BQ5:BQ30,"חופשה")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BR44" s="39">
         <f>COUNTIF(BR5:BR30,"חופשה")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="BS44" s="39">
         <f>COUNTIF(BS5:BS30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BT44" s="39">
         <f>COUNTIF(BT5:BT30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BU44" s="39">
         <f>COUNTIF(BU5:BU30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BV44" s="39">
         <f>COUNTIF(BV5:BV30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BW44" s="39">
         <f>COUNTIF(BW5:BW30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX44" s="39">
         <f>COUNTIF(BX5:BX30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BY44" s="39">
         <f>COUNTIF(BY5:BY30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BZ44" s="39">
         <f>COUNTIF(BZ5:BZ30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CA44" s="39">
         <f>COUNTIF(CA5:CA30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CB44" s="39">
         <f>COUNTIF(CB5:CB30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CC44" s="39">
         <f>COUNTIF(CC5:CC30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CD44" s="39">
         <f>COUNTIF(CD5:CD30,"חופשה")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="CE44" s="39">
         <f>COUNTIF(CE5:CE30,"חופשה")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="CF44" s="39">
         <f>COUNTIF(CF5:CF30,"חופשה")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="CG44" s="39">
         <f>COUNTIF(CG5:CG30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CH44" s="39">
         <f>COUNTIF(CH5:CH30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CI44" s="39">
         <f>COUNTIF(CI5:CI30,"חופשה")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="CJ44" s="39">
         <f>COUNTIF(CJ5:CJ30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK44" s="39">
         <f>COUNTIF(CK5:CK30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CL44" s="39">
         <f>COUNTIF(CL5:CL30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CM44" s="39">
         <f>COUNTIF(CM5:CM30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CN44" s="39">
         <f>COUNTIF(CN5:CN30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CO44" s="39">
         <f>COUNTIF(CO5:CO30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CP44" s="39">
         <f>COUNTIF(CP5:CP30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CQ44" s="39">
         <f>COUNTIF(CQ5:CQ30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CR44" s="39">
         <f>COUNTIF(CR5:CR30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CS44" s="39">
         <f>COUNTIF(CS5:CS30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CT44" s="39">
         <f>COUNTIF(CT5:CT30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CU44" s="39">
         <f>COUNTIF(CU5:CU30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CV44" s="39">
         <f>COUNTIF(CV5:CV30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CW44" s="39">
         <f>COUNTIF(CW5:CW30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CX44" s="39">
         <f>COUNTIF(CX5:CX30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CY44" s="39">
         <f>COUNTIF(CY5:CY30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CZ44" s="39">
         <f>COUNTIF(CZ5:CZ30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DA44" s="39">
         <f>COUNTIF(DA5:DA30,"חופשה")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -11680,411 +11680,411 @@
       </c>
       <c r="D45" s="39">
         <f>COUNTIF(D5:D30,"ת״ש")</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="E45" s="39">
         <f>COUNTIF(E5:E30,"ת״ש")</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="F45" s="39">
         <f>COUNTIF(F5:F30,"ת״ש")</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="G45" s="39">
         <f>COUNTIF(G5:G30,"ת״ש")</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="H45" s="39">
         <f>COUNTIF(H5:H30,"ת״ש")</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="I45" s="39">
         <f>COUNTIF(I5:I30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J45" s="39">
         <f>COUNTIF(J5:J30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K45" s="39">
         <f>COUNTIF(K5:K30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L45" s="39">
         <f>COUNTIF(L5:L30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M45" s="39">
         <f>COUNTIF(M5:M30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N45" s="39">
         <f>COUNTIF(N5:N30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O45" s="39">
         <f>COUNTIF(O5:O30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P45" s="39">
         <f>COUNTIF(P5:P30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q45" s="39">
         <f>COUNTIF(Q5:Q30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R45" s="39">
         <f>COUNTIF(R5:R30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S45" s="39">
         <f>COUNTIF(S5:S30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T45" s="39">
         <f>COUNTIF(T5:T30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U45" s="39">
         <f>COUNTIF(U5:U30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V45" s="39">
         <f>COUNTIF(V5:V30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W45" s="39">
         <f>COUNTIF(W5:W30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X45" s="39">
         <f>COUNTIF(X5:X30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y45" s="39">
         <f>COUNTIF(Y5:Y30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Z45" s="39">
         <f>COUNTIF(Z5:Z30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA45" s="39">
         <f>COUNTIF(AA5:AA30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AB45" s="39">
         <f>COUNTIF(AB5:AB30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC45" s="39">
         <f>COUNTIF(AC5:AC30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD45" s="39">
         <f>COUNTIF(AD5:AD30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE45" s="39">
         <f>COUNTIF(AE5:AE30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF45" s="39">
         <f>COUNTIF(AF5:AF30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG45" s="39">
         <f>COUNTIF(AG5:AG30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AH45" s="39">
         <f>COUNTIF(AH5:AH30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI45" s="39">
         <f>COUNTIF(AI5:AI30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ45" s="39">
         <f>COUNTIF(AJ5:AJ30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK45" s="39">
         <f>COUNTIF(AK5:AK30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL45" s="39">
         <f>COUNTIF(AL5:AL30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM45" s="39">
         <f>COUNTIF(AM5:AM30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AN45" s="39">
         <f>COUNTIF(AN5:AN30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO45" s="39">
         <f>COUNTIF(AO5:AO30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AP45" s="39">
         <f>COUNTIF(AP5:AP30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ45" s="39">
         <f>COUNTIF(AQ5:AQ30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AR45" s="39">
         <f>COUNTIF(AR5:AR30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS45" s="39">
         <f>COUNTIF(AS5:AS30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT45" s="39">
         <f>COUNTIF(AT5:AT30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU45" s="39">
         <f>COUNTIF(AU5:AU30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AV45" s="39">
         <f>COUNTIF(AV5:AV30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AW45" s="39">
         <f>COUNTIF(AW5:AW30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AX45" s="39">
         <f>COUNTIF(AX5:AX30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AY45" s="39">
         <f>COUNTIF(AY5:AY30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AZ45" s="39">
         <f>COUNTIF(AZ5:AZ30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BA45" s="39">
         <f>COUNTIF(BA5:BA30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB45" s="39">
         <f>COUNTIF(BB5:BB30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC45" s="39">
         <f>COUNTIF(BC5:BC30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD45" s="39">
         <f>COUNTIF(BD5:BD30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BE45" s="39">
         <f>COUNTIF(BE5:BE30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BF45" s="39">
         <f>COUNTIF(BF5:BF30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BG45" s="39">
         <f>COUNTIF(BG5:BG30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH45" s="39">
         <f>COUNTIF(BH5:BH30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BI45" s="39">
         <f>COUNTIF(BI5:BI30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BJ45" s="39">
         <f>COUNTIF(BJ5:BJ30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK45" s="39">
         <f>COUNTIF(BK5:BK30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL45" s="39">
         <f>COUNTIF(BL5:BL30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BM45" s="39">
         <f>COUNTIF(BM5:BM30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BN45" s="39">
         <f>COUNTIF(BN5:BN30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BO45" s="39">
         <f>COUNTIF(BO5:BO30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BP45" s="39">
         <f>COUNTIF(BP5:BP30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ45" s="39">
         <f>COUNTIF(BQ5:BQ30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BR45" s="39">
         <f>COUNTIF(BR5:BR30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BS45" s="39">
         <f>COUNTIF(BS5:BS30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BT45" s="39">
         <f>COUNTIF(BT5:BT30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BU45" s="39">
         <f>COUNTIF(BU5:BU30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BV45" s="39">
         <f>COUNTIF(BV5:BV30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BW45" s="39">
         <f>COUNTIF(BW5:BW30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX45" s="39">
         <f>COUNTIF(BX5:BX30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BY45" s="39">
         <f>COUNTIF(BY5:BY30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BZ45" s="39">
         <f>COUNTIF(BZ5:BZ30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CA45" s="39">
         <f>COUNTIF(CA5:CA30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CB45" s="39">
         <f>COUNTIF(CB5:CB30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CC45" s="39">
         <f>COUNTIF(CC5:CC30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CD45" s="39">
         <f>COUNTIF(CD5:CD30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE45" s="39">
         <f>COUNTIF(CE5:CE30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CF45" s="39">
         <f>COUNTIF(CF5:CF30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CG45" s="39">
         <f>COUNTIF(CG5:CG30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CH45" s="39">
         <f>COUNTIF(CH5:CH30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CI45" s="39">
         <f>COUNTIF(CI5:CI30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CJ45" s="39">
         <f>COUNTIF(CJ5:CJ30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK45" s="39">
         <f>COUNTIF(CK5:CK30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CL45" s="39">
         <f>COUNTIF(CL5:CL30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CM45" s="39">
         <f>COUNTIF(CM5:CM30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CN45" s="39">
         <f>COUNTIF(CN5:CN30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CO45" s="39">
         <f>COUNTIF(CO5:CO30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CP45" s="39">
         <f>COUNTIF(CP5:CP30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CQ45" s="39">
         <f>COUNTIF(CQ5:CQ30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CR45" s="39">
         <f>COUNTIF(CR5:CR30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CS45" s="39">
         <f>COUNTIF(CS5:CS30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CT45" s="39">
         <f>COUNTIF(CT5:CT30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CU45" s="39">
         <f>COUNTIF(CU5:CU30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CV45" s="39">
         <f>COUNTIF(CV5:CV30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CW45" s="39">
         <f>COUNTIF(CW5:CW30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CX45" s="39">
         <f>COUNTIF(CX5:CX30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CY45" s="39">
         <f>COUNTIF(CY5:CY30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CZ45" s="39">
         <f>COUNTIF(CZ5:CZ30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DA45" s="39">
         <f>COUNTIF(DA5:DA30,"ת״ש")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -12095,411 +12095,411 @@
       </c>
       <c r="D46" s="39">
         <f>COUNTIF(D5:D30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E46" s="39">
         <f>COUNTIF(E5:E30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F46" s="39">
         <f>COUNTIF(F5:F30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G46" s="39">
         <f>COUNTIF(G5:G30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H46" s="39">
         <f>COUNTIF(H5:H30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I46" s="39">
         <f>COUNTIF(I5:I30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J46" s="39">
         <f>COUNTIF(J5:J30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K46" s="39">
         <f>COUNTIF(K5:K30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L46" s="39">
         <f>COUNTIF(L5:L30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M46" s="39">
         <f>COUNTIF(M5:M30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N46" s="39">
         <f>COUNTIF(N5:N30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O46" s="39">
         <f>COUNTIF(O5:O30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P46" s="39">
         <f>COUNTIF(P5:P30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q46" s="39">
         <f>COUNTIF(Q5:Q30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R46" s="39">
         <f>COUNTIF(R5:R30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="S46" s="39">
         <f>COUNTIF(S5:S30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T46" s="39">
         <f>COUNTIF(T5:T30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U46" s="39">
         <f>COUNTIF(U5:U30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V46" s="39">
         <f>COUNTIF(V5:V30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="W46" s="39">
         <f>COUNTIF(W5:W30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="X46" s="39">
         <f>COUNTIF(X5:X30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y46" s="39">
         <f>COUNTIF(Y5:Y30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Z46" s="39">
         <f>COUNTIF(Z5:Z30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA46" s="39">
         <f>COUNTIF(AA5:AA30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AB46" s="39">
         <f>COUNTIF(AB5:AB30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC46" s="39">
         <f>COUNTIF(AC5:AC30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD46" s="39">
         <f>COUNTIF(AD5:AD30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AE46" s="39">
         <f>COUNTIF(AE5:AE30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AF46" s="39">
         <f>COUNTIF(AF5:AF30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AG46" s="39">
         <f>COUNTIF(AG5:AG30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AH46" s="39">
         <f>COUNTIF(AH5:AH30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AI46" s="39">
         <f>COUNTIF(AI5:AI30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AJ46" s="39">
         <f>COUNTIF(AJ5:AJ30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AK46" s="39">
         <f>COUNTIF(AK5:AK30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AL46" s="39">
         <f>COUNTIF(AL5:AL30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AM46" s="39">
         <f>COUNTIF(AM5:AM30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AN46" s="39">
         <f>COUNTIF(AN5:AN30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AO46" s="39">
         <f>COUNTIF(AO5:AO30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AP46" s="39">
         <f>COUNTIF(AP5:AP30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AQ46" s="39">
         <f>COUNTIF(AQ5:AQ30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AR46" s="39">
         <f>COUNTIF(AR5:AR30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AS46" s="39">
         <f>COUNTIF(AS5:AS30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AT46" s="39">
         <f>COUNTIF(AT5:AT30,"קורס")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AU46" s="39">
         <f>COUNTIF(AU5:AU30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AV46" s="39">
         <f>COUNTIF(AV5:AV30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AW46" s="39">
         <f>COUNTIF(AW5:AW30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AX46" s="39">
         <f>COUNTIF(AX5:AX30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AY46" s="39">
         <f>COUNTIF(AY5:AY30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AZ46" s="39">
         <f>COUNTIF(AZ5:AZ30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BA46" s="39">
         <f>COUNTIF(BA5:BA30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB46" s="39">
         <f>COUNTIF(BB5:BB30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC46" s="39">
         <f>COUNTIF(BC5:BC30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD46" s="39">
         <f>COUNTIF(BD5:BD30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BE46" s="39">
         <f>COUNTIF(BE5:BE30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BF46" s="39">
         <f>COUNTIF(BF5:BF30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BG46" s="39">
         <f>COUNTIF(BG5:BG30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH46" s="39">
         <f>COUNTIF(BH5:BH30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BI46" s="39">
         <f>COUNTIF(BI5:BI30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BJ46" s="39">
         <f>COUNTIF(BJ5:BJ30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK46" s="39">
         <f>COUNTIF(BK5:BK30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL46" s="39">
         <f>COUNTIF(BL5:BL30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BM46" s="39">
         <f>COUNTIF(BM5:BM30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BN46" s="39">
         <f>COUNTIF(BN5:BN30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BO46" s="39">
         <f>COUNTIF(BO5:BO30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BP46" s="39">
         <f>COUNTIF(BP5:BP30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ46" s="39">
         <f>COUNTIF(BQ5:BQ30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BR46" s="39">
         <f>COUNTIF(BR5:BR30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BS46" s="39">
         <f>COUNTIF(BS5:BS30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BT46" s="39">
         <f>COUNTIF(BT5:BT30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BU46" s="39">
         <f>COUNTIF(BU5:BU30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BV46" s="39">
         <f>COUNTIF(BV5:BV30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BW46" s="39">
         <f>COUNTIF(BW5:BW30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX46" s="39">
         <f>COUNTIF(BX5:BX30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BY46" s="39">
         <f>COUNTIF(BY5:BY30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BZ46" s="39">
         <f>COUNTIF(BZ5:BZ30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CA46" s="39">
         <f>COUNTIF(CA5:CA30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CB46" s="39">
         <f>COUNTIF(CB5:CB30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CC46" s="39">
         <f>COUNTIF(CC5:CC30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CD46" s="39">
         <f>COUNTIF(CD5:CD30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE46" s="39">
         <f>COUNTIF(CE5:CE30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CF46" s="39">
         <f>COUNTIF(CF5:CF30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CG46" s="39">
         <f>COUNTIF(CG5:CG30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CH46" s="39">
         <f>COUNTIF(CH5:CH30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CI46" s="39">
         <f>COUNTIF(CI5:CI30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CJ46" s="39">
         <f>COUNTIF(CJ5:CJ30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK46" s="39">
         <f>COUNTIF(CK5:CK30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CL46" s="39">
         <f>COUNTIF(CL5:CL30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CM46" s="39">
         <f>COUNTIF(CM5:CM30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CN46" s="39">
         <f>COUNTIF(CN5:CN30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CO46" s="39">
         <f>COUNTIF(CO5:CO30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CP46" s="39">
         <f>COUNTIF(CP5:CP30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CQ46" s="39">
         <f>COUNTIF(CQ5:CQ30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CR46" s="39">
         <f>COUNTIF(CR5:CR30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CS46" s="39">
         <f>COUNTIF(CS5:CS30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CT46" s="39">
         <f>COUNTIF(CT5:CT30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CU46" s="39">
         <f>COUNTIF(CU5:CU30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CV46" s="39">
         <f>COUNTIF(CV5:CV30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CW46" s="39">
         <f>COUNTIF(CW5:CW30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CX46" s="39">
         <f>COUNTIF(CX5:CX30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CY46" s="39">
         <f>COUNTIF(CY5:CY30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CZ46" s="39">
         <f>COUNTIF(CZ5:CZ30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DA46" s="39">
         <f>COUNTIF(DA5:DA30,"קורס")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -12510,411 +12510,411 @@
       </c>
       <c r="D47" s="39">
         <f>COUNTIF(D5:D30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E47" s="39">
         <f>COUNTIF(E5:E30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F47" s="39">
         <f>COUNTIF(F5:F30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G47" s="39">
         <f>COUNTIF(G5:G30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H47" s="39">
         <f>COUNTIF(H5:H30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I47" s="39">
         <f>COUNTIF(I5:I30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J47" s="39">
         <f>COUNTIF(J5:J30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K47" s="39">
         <f>COUNTIF(K5:K30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L47" s="39">
         <f>COUNTIF(L5:L30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M47" s="39">
         <f>COUNTIF(M5:M30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N47" s="39">
         <f>COUNTIF(N5:N30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O47" s="39">
         <f>COUNTIF(O5:O30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P47" s="39">
         <f>COUNTIF(P5:P30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q47" s="39">
         <f>COUNTIF(Q5:Q30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R47" s="39">
         <f>COUNTIF(R5:R30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S47" s="39">
         <f>COUNTIF(S5:S30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T47" s="39">
         <f>COUNTIF(T5:T30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U47" s="39">
         <f>COUNTIF(U5:U30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V47" s="39">
         <f>COUNTIF(V5:V30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W47" s="39">
         <f>COUNTIF(W5:W30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X47" s="39">
         <f>COUNTIF(X5:X30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y47" s="39">
         <f>COUNTIF(Y5:Y30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Z47" s="39">
         <f>COUNTIF(Z5:Z30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA47" s="39">
         <f>COUNTIF(AA5:AA30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AB47" s="39">
         <f>COUNTIF(AB5:AB30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC47" s="39">
         <f>COUNTIF(AC5:AC30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD47" s="39">
         <f>COUNTIF(AD5:AD30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE47" s="39">
         <f>COUNTIF(AE5:AE30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF47" s="39">
         <f>COUNTIF(AF5:AF30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG47" s="39">
         <f>COUNTIF(AG5:AG30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AH47" s="39">
         <f>COUNTIF(AH5:AH30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI47" s="39">
         <f>COUNTIF(AI5:AI30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ47" s="39">
         <f>COUNTIF(AJ5:AJ30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK47" s="39">
         <f>COUNTIF(AK5:AK30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL47" s="39">
         <f>COUNTIF(AL5:AL30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM47" s="39">
         <f>COUNTIF(AM5:AM30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AN47" s="39">
         <f>COUNTIF(AN5:AN30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO47" s="39">
         <f>COUNTIF(AO5:AO30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AP47" s="39">
         <f>COUNTIF(AP5:AP30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ47" s="39">
         <f>COUNTIF(AQ5:AQ30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AR47" s="39">
         <f>COUNTIF(AR5:AR30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS47" s="39">
         <f>COUNTIF(AS5:AS30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT47" s="39">
         <f>COUNTIF(AT5:AT30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU47" s="39">
         <f>COUNTIF(AU5:AU30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AV47" s="39">
         <f>COUNTIF(AV5:AV30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AW47" s="39">
         <f>COUNTIF(AW5:AW30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AX47" s="39">
         <f>COUNTIF(AX5:AX30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AY47" s="39">
         <f>COUNTIF(AY5:AY30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AZ47" s="39">
         <f>COUNTIF(AZ5:AZ30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BA47" s="39">
         <f>COUNTIF(BA5:BA30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB47" s="39">
         <f>COUNTIF(BB5:BB30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC47" s="39">
         <f>COUNTIF(BC5:BC30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD47" s="39">
         <f>COUNTIF(BD5:BD30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BE47" s="39">
         <f>COUNTIF(BE5:BE30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BF47" s="39">
         <f>COUNTIF(BF5:BF30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BG47" s="39">
         <f>COUNTIF(BG5:BG30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH47" s="39">
         <f>COUNTIF(BH5:BH30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BI47" s="39">
         <f>COUNTIF(BI5:BI30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BJ47" s="39">
         <f>COUNTIF(BJ5:BJ30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK47" s="39">
         <f>COUNTIF(BK5:BK30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL47" s="39">
         <f>COUNTIF(BL5:BL30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BM47" s="39">
         <f>COUNTIF(BM5:BM30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BN47" s="39">
         <f>COUNTIF(BN5:BN30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BO47" s="39">
         <f>COUNTIF(BO5:BO30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BP47" s="39">
         <f>COUNTIF(BP5:BP30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ47" s="39">
         <f>COUNTIF(BQ5:BQ30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BR47" s="39">
         <f>COUNTIF(BR5:BR30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BS47" s="39">
         <f>COUNTIF(BS5:BS30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BT47" s="39">
         <f>COUNTIF(BT5:BT30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BU47" s="39">
         <f>COUNTIF(BU5:BU30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BV47" s="39">
         <f>COUNTIF(BV5:BV30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BW47" s="39">
         <f>COUNTIF(BW5:BW30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX47" s="39">
         <f>COUNTIF(BX5:BX30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BY47" s="39">
         <f>COUNTIF(BY5:BY30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BZ47" s="39">
         <f>COUNTIF(BZ5:BZ30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CA47" s="39">
         <f>COUNTIF(CA5:CA30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CB47" s="39">
         <f>COUNTIF(CB5:CB30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CC47" s="39">
         <f>COUNTIF(CC5:CC30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CD47" s="39">
         <f>COUNTIF(CD5:CD30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE47" s="39">
         <f>COUNTIF(CE5:CE30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CF47" s="39">
         <f>COUNTIF(CF5:CF30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CG47" s="39">
         <f>COUNTIF(CG5:CG30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CH47" s="39">
         <f>COUNTIF(CH5:CH30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CI47" s="39">
         <f>COUNTIF(CI5:CI30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CJ47" s="39">
         <f>COUNTIF(CJ5:CJ30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK47" s="39">
         <f>COUNTIF(CK5:CK30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CL47" s="39">
         <f>COUNTIF(CL5:CL30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CM47" s="39">
         <f>COUNTIF(CM5:CM30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CN47" s="39">
         <f>COUNTIF(CN5:CN30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CO47" s="39">
         <f>COUNTIF(CO5:CO30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CP47" s="39">
         <f>COUNTIF(CP5:CP30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CQ47" s="39">
         <f>COUNTIF(CQ5:CQ30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CR47" s="39">
         <f>COUNTIF(CR5:CR30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CS47" s="39">
         <f>COUNTIF(CS5:CS30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CT47" s="39">
         <f>COUNTIF(CT5:CT30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CU47" s="39">
         <f>COUNTIF(CU5:CU30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CV47" s="39">
         <f>COUNTIF(CV5:CV30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CW47" s="39">
         <f>COUNTIF(CW5:CW30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CX47" s="39">
         <f>COUNTIF(CX5:CX30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CY47" s="39">
         <f>COUNTIF(CY5:CY30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CZ47" s="39">
         <f>COUNTIF(CZ5:CZ30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DA47" s="39">
         <f>COUNTIF(DA5:DA30,"גימלים")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -12925,411 +12925,411 @@
       </c>
       <c r="D48" s="39">
         <f>COUNTIF(D5:D30,"מבחן")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E48" s="39">
         <f>COUNTIF(E5:E30,"מבחן")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F48" s="39">
         <f>COUNTIF(F5:F30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G48" s="39">
         <f>COUNTIF(G5:G30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="39">
         <f>COUNTIF(H5:H30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I48" s="39">
         <f>COUNTIF(I5:I30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J48" s="39">
         <f>COUNTIF(J5:J30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K48" s="39">
         <f>COUNTIF(K5:K30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L48" s="39">
         <f>COUNTIF(L5:L30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M48" s="39">
         <f>COUNTIF(M5:M30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N48" s="39">
         <f>COUNTIF(N5:N30,"מבחן")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O48" s="39">
         <f>COUNTIF(O5:O30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P48" s="39">
         <f>COUNTIF(P5:P30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q48" s="39">
         <f>COUNTIF(Q5:Q30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R48" s="39">
         <f>COUNTIF(R5:R30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S48" s="39">
         <f>COUNTIF(S5:S30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T48" s="39">
         <f>COUNTIF(T5:T30,"מבחן")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U48" s="39">
         <f>COUNTIF(U5:U30,"מבחן")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V48" s="39">
         <f>COUNTIF(V5:V30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W48" s="39">
         <f>COUNTIF(W5:W30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X48" s="39">
         <f>COUNTIF(X5:X30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y48" s="39">
         <f>COUNTIF(Y5:Y30,"מבחן")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Z48" s="39">
         <f>COUNTIF(Z5:Z30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA48" s="39">
         <f>COUNTIF(AA5:AA30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AB48" s="39">
         <f>COUNTIF(AB5:AB30,"מבחן")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC48" s="39">
         <f>COUNTIF(AC5:AC30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD48" s="39">
         <f>COUNTIF(AD5:AD30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE48" s="39">
         <f>COUNTIF(AE5:AE30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF48" s="39">
         <f>COUNTIF(AF5:AF30,"מבחן")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AG48" s="39">
         <f>COUNTIF(AG5:AG30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AH48" s="39">
         <f>COUNTIF(AH5:AH30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI48" s="39">
         <f>COUNTIF(AI5:AI30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ48" s="39">
         <f>COUNTIF(AJ5:AJ30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK48" s="39">
         <f>COUNTIF(AK5:AK30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL48" s="39">
         <f>COUNTIF(AL5:AL30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM48" s="39">
         <f>COUNTIF(AM5:AM30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AN48" s="39">
         <f>COUNTIF(AN5:AN30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO48" s="39">
         <f>COUNTIF(AO5:AO30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AP48" s="39">
         <f>COUNTIF(AP5:AP30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ48" s="39">
         <f>COUNTIF(AQ5:AQ30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AR48" s="39">
         <f>COUNTIF(AR5:AR30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS48" s="39">
         <f>COUNTIF(AS5:AS30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT48" s="39">
         <f>COUNTIF(AT5:AT30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU48" s="39">
         <f>COUNTIF(AU5:AU30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AV48" s="39">
         <f>COUNTIF(AV5:AV30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AW48" s="39">
         <f>COUNTIF(AW5:AW30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AX48" s="39">
         <f>COUNTIF(AX5:AX30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AY48" s="39">
         <f>COUNTIF(AY5:AY30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AZ48" s="39">
         <f>COUNTIF(AZ5:AZ30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BA48" s="39">
         <f>COUNTIF(BA5:BA30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB48" s="39">
         <f>COUNTIF(BB5:BB30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC48" s="39">
         <f>COUNTIF(BC5:BC30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD48" s="39">
         <f>COUNTIF(BD5:BD30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BE48" s="39">
         <f>COUNTIF(BE5:BE30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BF48" s="39">
         <f>COUNTIF(BF5:BF30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BG48" s="39">
         <f>COUNTIF(BG5:BG30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH48" s="39">
         <f>COUNTIF(BH5:BH30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BI48" s="39">
         <f>COUNTIF(BI5:BI30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BJ48" s="39">
         <f>COUNTIF(BJ5:BJ30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK48" s="39">
         <f>COUNTIF(BK5:BK30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL48" s="39">
         <f>COUNTIF(BL5:BL30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BM48" s="39">
         <f>COUNTIF(BM5:BM30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BN48" s="39">
         <f>COUNTIF(BN5:BN30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BO48" s="39">
         <f>COUNTIF(BO5:BO30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BP48" s="39">
         <f>COUNTIF(BP5:BP30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ48" s="39">
         <f>COUNTIF(BQ5:BQ30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BR48" s="39">
         <f>COUNTIF(BR5:BR30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BS48" s="39">
         <f>COUNTIF(BS5:BS30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BT48" s="39">
         <f>COUNTIF(BT5:BT30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BU48" s="39">
         <f>COUNTIF(BU5:BU30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BV48" s="39">
         <f>COUNTIF(BV5:BV30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BW48" s="39">
         <f>COUNTIF(BW5:BW30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX48" s="39">
         <f>COUNTIF(BX5:BX30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BY48" s="39">
         <f>COUNTIF(BY5:BY30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BZ48" s="39">
         <f>COUNTIF(BZ5:BZ30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CA48" s="39">
         <f>COUNTIF(CA5:CA30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CB48" s="39">
         <f>COUNTIF(CB5:CB30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CC48" s="39">
         <f>COUNTIF(CC5:CC30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CD48" s="39">
         <f>COUNTIF(CD5:CD30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE48" s="39">
         <f>COUNTIF(CE5:CE30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CF48" s="39">
         <f>COUNTIF(CF5:CF30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CG48" s="39">
         <f>COUNTIF(CG5:CG30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CH48" s="39">
         <f>COUNTIF(CH5:CH30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CI48" s="39">
         <f>COUNTIF(CI5:CI30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CJ48" s="39">
         <f>COUNTIF(CJ5:CJ30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK48" s="39">
         <f>COUNTIF(CK5:CK30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CL48" s="39">
         <f>COUNTIF(CL5:CL30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CM48" s="39">
         <f>COUNTIF(CM5:CM30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CN48" s="39">
         <f>COUNTIF(CN5:CN30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CO48" s="39">
         <f>COUNTIF(CO5:CO30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CP48" s="39">
         <f>COUNTIF(CP5:CP30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CQ48" s="39">
         <f>COUNTIF(CQ5:CQ30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CR48" s="39">
         <f>COUNTIF(CR5:CR30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CS48" s="39">
         <f>COUNTIF(CS5:CS30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CT48" s="39">
         <f>COUNTIF(CT5:CT30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CU48" s="39">
         <f>COUNTIF(CU5:CU30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CV48" s="39">
         <f>COUNTIF(CV5:CV30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CW48" s="39">
         <f>COUNTIF(CW5:CW30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CX48" s="39">
         <f>COUNTIF(CX5:CX30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CY48" s="39">
         <f>COUNTIF(CY5:CY30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CZ48" s="39">
         <f>COUNTIF(CZ5:CZ30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DA48" s="39">
         <f>COUNTIF(DA5:DA30,"מבחן")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -13340,411 +13340,411 @@
       </c>
       <c r="D49" s="39">
         <f>COUNTIF(D5:D30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E49" s="39">
         <f>COUNTIF(E5:E30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F49" s="39">
         <f>COUNTIF(F5:F30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G49" s="39">
         <f>COUNTIF(G5:G30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H49" s="39">
         <f>COUNTIF(H5:H30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I49" s="39">
         <f>COUNTIF(I5:I30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J49" s="39">
         <f>COUNTIF(J5:J30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K49" s="39">
         <f>COUNTIF(K5:K30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L49" s="39">
         <f>COUNTIF(L5:L30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M49" s="39">
         <f>COUNTIF(M5:M30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N49" s="39">
         <f>COUNTIF(N5:N30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O49" s="39">
         <f>COUNTIF(O5:O30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P49" s="39">
         <f>COUNTIF(P5:P30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q49" s="39">
         <f>COUNTIF(Q5:Q30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R49" s="39">
         <f>COUNTIF(R5:R30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S49" s="39">
         <f>COUNTIF(S5:S30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T49" s="39">
         <f>COUNTIF(T5:T30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U49" s="39">
         <f>COUNTIF(U5:U30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V49" s="39">
         <f>COUNTIF(V5:V30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W49" s="39">
         <f>COUNTIF(W5:W30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X49" s="39">
         <f>COUNTIF(X5:X30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y49" s="39">
         <f>COUNTIF(Y5:Y30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Z49" s="39">
         <f>COUNTIF(Z5:Z30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA49" s="39">
         <f>COUNTIF(AA5:AA30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AB49" s="39">
         <f>COUNTIF(AB5:AB30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC49" s="39">
         <f>COUNTIF(AC5:AC30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD49" s="39">
         <f>COUNTIF(AD5:AD30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE49" s="39">
         <f>COUNTIF(AE5:AE30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF49" s="39">
         <f>COUNTIF(AF5:AF30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG49" s="39">
         <f>COUNTIF(AG5:AG30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AH49" s="39">
         <f>COUNTIF(AH5:AH30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI49" s="39">
         <f>COUNTIF(AI5:AI30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ49" s="39">
         <f>COUNTIF(AJ5:AJ30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK49" s="39">
         <f>COUNTIF(AK5:AK30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL49" s="39">
         <f>COUNTIF(AL5:AL30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM49" s="39">
         <f>COUNTIF(AM5:AM30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AN49" s="39">
         <f>COUNTIF(AN5:AN30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO49" s="39">
         <f>COUNTIF(AO5:AO30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AP49" s="39">
         <f>COUNTIF(AP5:AP30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ49" s="39">
         <f>COUNTIF(AQ5:AQ30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AR49" s="39">
         <f>COUNTIF(AR5:AR30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS49" s="39">
         <f>COUNTIF(AS5:AS30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT49" s="39">
         <f>COUNTIF(AT5:AT30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU49" s="39">
         <f>COUNTIF(AU5:AU30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AV49" s="39">
         <f>COUNTIF(AV5:AV30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AW49" s="39">
         <f>COUNTIF(AW5:AW30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AX49" s="39">
         <f>COUNTIF(AX5:AX30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AY49" s="39">
         <f>COUNTIF(AY5:AY30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AZ49" s="39">
         <f>COUNTIF(AZ5:AZ30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BA49" s="39">
         <f>COUNTIF(BA5:BA30,"חול")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BB49" s="39">
         <f>COUNTIF(BB5:BB30,"חול")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BC49" s="39">
         <f>COUNTIF(BC5:BC30,"חול")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BD49" s="39">
         <f>COUNTIF(BD5:BD30,"חול")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BE49" s="39">
         <f>COUNTIF(BE5:BE30,"חול")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BF49" s="39">
         <f>COUNTIF(BF5:BF30,"חול")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BG49" s="39">
         <f>COUNTIF(BG5:BG30,"חול")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="BH49" s="39">
         <f>COUNTIF(BH5:BH30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BI49" s="39">
         <f>COUNTIF(BI5:BI30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BJ49" s="39">
         <f>COUNTIF(BJ5:BJ30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK49" s="39">
         <f>COUNTIF(BK5:BK30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL49" s="39">
         <f>COUNTIF(BL5:BL30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BM49" s="39">
         <f>COUNTIF(BM5:BM30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BN49" s="39">
         <f>COUNTIF(BN5:BN30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BO49" s="39">
         <f>COUNTIF(BO5:BO30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BP49" s="39">
         <f>COUNTIF(BP5:BP30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ49" s="39">
         <f>COUNTIF(BQ5:BQ30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BR49" s="39">
         <f>COUNTIF(BR5:BR30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BS49" s="39">
         <f>COUNTIF(BS5:BS30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BT49" s="39">
         <f>COUNTIF(BT5:BT30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BU49" s="39">
         <f>COUNTIF(BU5:BU30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BV49" s="39">
         <f>COUNTIF(BV5:BV30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BW49" s="39">
         <f>COUNTIF(BW5:BW30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX49" s="39">
         <f>COUNTIF(BX5:BX30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BY49" s="39">
         <f>COUNTIF(BY5:BY30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BZ49" s="39">
         <f>COUNTIF(BZ5:BZ30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CA49" s="39">
         <f>COUNTIF(CA5:CA30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CB49" s="39">
         <f>COUNTIF(CB5:CB30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CC49" s="39">
         <f>COUNTIF(CC5:CC30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CD49" s="39">
         <f>COUNTIF(CD5:CD30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE49" s="39">
         <f>COUNTIF(CE5:CE30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CF49" s="39">
         <f>COUNTIF(CF5:CF30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CG49" s="39">
         <f>COUNTIF(CG5:CG30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CH49" s="39">
         <f>COUNTIF(CH5:CH30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CI49" s="39">
         <f>COUNTIF(CI5:CI30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CJ49" s="39">
         <f>COUNTIF(CJ5:CJ30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK49" s="39">
         <f>COUNTIF(CK5:CK30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CL49" s="39">
         <f>COUNTIF(CL5:CL30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CM49" s="39">
         <f>COUNTIF(CM5:CM30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CN49" s="39">
         <f>COUNTIF(CN5:CN30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CO49" s="39">
         <f>COUNTIF(CO5:CO30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CP49" s="39">
         <f>COUNTIF(CP5:CP30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CQ49" s="39">
         <f>COUNTIF(CQ5:CQ30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CR49" s="39">
         <f>COUNTIF(CR5:CR30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CS49" s="39">
         <f>COUNTIF(CS5:CS30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CT49" s="39">
         <f>COUNTIF(CT5:CT30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CU49" s="39">
         <f>COUNTIF(CU5:CU30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CV49" s="39">
         <f>COUNTIF(CV5:CV30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CW49" s="39">
         <f>COUNTIF(CW5:CW30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CX49" s="39">
         <f>COUNTIF(CX5:CX30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CY49" s="39">
         <f>COUNTIF(CY5:CY30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CZ49" s="39">
         <f>COUNTIF(CZ5:CZ30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DA49" s="39">
         <f>COUNTIF(DA5:DA30,"חול")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -13755,411 +13755,411 @@
       </c>
       <c r="D50" s="39">
         <f>COUNTIF(D5:D30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E50" s="39">
         <f>COUNTIF(E5:E30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F50" s="39">
         <f>COUNTIF(F5:F30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G50" s="39">
         <f>COUNTIF(G5:G30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H50" s="39">
         <f>COUNTIF(H5:H30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I50" s="39">
         <f>COUNTIF(I5:I30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J50" s="39">
         <f>COUNTIF(J5:J30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K50" s="39">
         <f>COUNTIF(K5:K30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L50" s="39">
         <f>COUNTIF(L5:L30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M50" s="39">
         <f>COUNTIF(M5:M30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N50" s="39">
         <f>COUNTIF(N5:N30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O50" s="39">
         <f>COUNTIF(O5:O30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P50" s="39">
         <f>COUNTIF(P5:P30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q50" s="39">
         <f>COUNTIF(Q5:Q30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R50" s="39">
         <f>COUNTIF(R5:R30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S50" s="39">
         <f>COUNTIF(S5:S30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T50" s="39">
         <f>COUNTIF(T5:T30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U50" s="39">
         <f>COUNTIF(U5:U30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V50" s="39">
         <f>COUNTIF(V5:V30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W50" s="39">
         <f>COUNTIF(W5:W30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X50" s="39">
         <f>COUNTIF(X5:X30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y50" s="39">
         <f>COUNTIF(Y5:Y30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Z50" s="39">
         <f>COUNTIF(Z5:Z30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA50" s="39">
         <f>COUNTIF(AA5:AA30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AB50" s="39">
         <f>COUNTIF(AB5:AB30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC50" s="39">
         <f>COUNTIF(AC5:AC30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD50" s="39">
         <f>COUNTIF(AD5:AD30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE50" s="39">
         <f>COUNTIF(AE5:AE30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF50" s="39">
         <f>COUNTIF(AF5:AF30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG50" s="39">
         <f>COUNTIF(AG5:AG30,"בית")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AH50" s="39">
         <f>COUNTIF(AH5:AH30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI50" s="39">
         <f>COUNTIF(AI5:AI30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ50" s="39">
         <f>COUNTIF(AJ5:AJ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK50" s="39">
         <f>COUNTIF(AK5:AK30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL50" s="39">
         <f>COUNTIF(AL5:AL30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM50" s="39">
         <f>COUNTIF(AM5:AM30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AN50" s="39">
         <f>COUNTIF(AN5:AN30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO50" s="39">
         <f>COUNTIF(AO5:AO30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AP50" s="39">
         <f>COUNTIF(AP5:AP30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ50" s="39">
         <f>COUNTIF(AQ5:AQ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AR50" s="39">
         <f>COUNTIF(AR5:AR30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS50" s="39">
         <f>COUNTIF(AS5:AS30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT50" s="39">
         <f>COUNTIF(AT5:AT30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU50" s="39">
         <f>COUNTIF(AU5:AU30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AV50" s="39">
         <f>COUNTIF(AV5:AV30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AW50" s="39">
         <f>COUNTIF(AW5:AW30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AX50" s="39">
         <f>COUNTIF(AX5:AX30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AY50" s="39">
         <f>COUNTIF(AY5:AY30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AZ50" s="39">
         <f>COUNTIF(AZ5:AZ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BA50" s="39">
         <f>COUNTIF(BA5:BA30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB50" s="39">
         <f>COUNTIF(BB5:BB30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC50" s="39">
         <f>COUNTIF(BC5:BC30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD50" s="39">
         <f>COUNTIF(BD5:BD30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BE50" s="39">
         <f>COUNTIF(BE5:BE30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BF50" s="39">
         <f>COUNTIF(BF5:BF30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BG50" s="39">
         <f>COUNTIF(BG5:BG30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH50" s="39">
         <f>COUNTIF(BH5:BH30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BI50" s="39">
         <f>COUNTIF(BI5:BI30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BJ50" s="39">
         <f>COUNTIF(BJ5:BJ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK50" s="39">
         <f>COUNTIF(BK5:BK30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL50" s="39">
         <f>COUNTIF(BL5:BL30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BM50" s="39">
         <f>COUNTIF(BM5:BM30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BN50" s="39">
         <f>COUNTIF(BN5:BN30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BO50" s="39">
         <f>COUNTIF(BO5:BO30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BP50" s="39">
         <f>COUNTIF(BP5:BP30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ50" s="39">
         <f>COUNTIF(BQ5:BQ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BR50" s="39">
         <f>COUNTIF(BR5:BR30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BS50" s="39">
         <f>COUNTIF(BS5:BS30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BT50" s="39">
         <f>COUNTIF(BT5:BT30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BU50" s="39">
         <f>COUNTIF(BU5:BU30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BV50" s="39">
         <f>COUNTIF(BV5:BV30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BW50" s="39">
         <f>COUNTIF(BW5:BW30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX50" s="39">
         <f>COUNTIF(BX5:BX30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BY50" s="39">
         <f>COUNTIF(BY5:BY30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BZ50" s="39">
         <f>COUNTIF(BZ5:BZ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CA50" s="39">
         <f>COUNTIF(CA5:CA30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CB50" s="39">
         <f>COUNTIF(CB5:CB30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CC50" s="39">
         <f>COUNTIF(CC5:CC30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CD50" s="39">
         <f>COUNTIF(CD5:CD30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE50" s="39">
         <f>COUNTIF(CE5:CE30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CF50" s="39">
         <f>COUNTIF(CF5:CF30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CG50" s="39">
         <f>COUNTIF(CG5:CG30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CH50" s="39">
         <f>COUNTIF(CH5:CH30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CI50" s="39">
         <f>COUNTIF(CI5:CI30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CJ50" s="39">
         <f>COUNTIF(CJ5:CJ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK50" s="39">
         <f>COUNTIF(CK5:CK30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CL50" s="39">
         <f>COUNTIF(CL5:CL30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CM50" s="39">
         <f>COUNTIF(CM5:CM30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CN50" s="39">
         <f>COUNTIF(CN5:CN30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CO50" s="39">
         <f>COUNTIF(CO5:CO30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CP50" s="39">
         <f>COUNTIF(CP5:CP30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CQ50" s="39">
         <f>COUNTIF(CQ5:CQ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CR50" s="39">
         <f>COUNTIF(CR5:CR30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CS50" s="39">
         <f>COUNTIF(CS5:CS30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CT50" s="39">
         <f>COUNTIF(CT5:CT30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CU50" s="39">
         <f>COUNTIF(CU5:CU30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CV50" s="39">
         <f>COUNTIF(CV5:CV30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CW50" s="39">
         <f>COUNTIF(CW5:CW30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CX50" s="39">
         <f>COUNTIF(CX5:CX30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CY50" s="39">
         <f>COUNTIF(CY5:CY30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CZ50" s="39">
         <f>COUNTIF(CZ5:CZ30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DA50" s="39">
         <f>COUNTIF(DA5:DA30,"בית")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -14170,411 +14170,411 @@
       </c>
       <c r="D51" s="39">
         <f>COUNTIF(D5:D30,"X")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="E51" s="39">
         <f>COUNTIF(E5:E30,"X")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="F51" s="39">
         <f>COUNTIF(F5:F30,"X")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G51" s="39">
         <f>COUNTIF(G5:G30,"X")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="H51" s="39">
         <f>COUNTIF(H5:H30,"X")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I51" s="39">
         <f>COUNTIF(I5:I30,"X")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J51" s="39">
         <f>COUNTIF(J5:J30,"X")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="K51" s="39">
         <f>COUNTIF(K5:K30,"X")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L51" s="39">
         <f>COUNTIF(L5:L30,"X")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M51" s="39">
         <f>COUNTIF(M5:M30,"X")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N51" s="39">
         <f>COUNTIF(N5:N30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O51" s="39">
         <f>COUNTIF(O5:O30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P51" s="39">
         <f>COUNTIF(P5:P30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q51" s="39">
         <f>COUNTIF(Q5:Q30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R51" s="39">
         <f>COUNTIF(R5:R30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S51" s="39">
         <f>COUNTIF(S5:S30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T51" s="39">
         <f>COUNTIF(T5:T30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U51" s="39">
         <f>COUNTIF(U5:U30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V51" s="39">
         <f>COUNTIF(V5:V30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W51" s="39">
         <f>COUNTIF(W5:W30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X51" s="39">
         <f>COUNTIF(X5:X30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y51" s="39">
         <f>COUNTIF(Y5:Y30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Z51" s="39">
         <f>COUNTIF(Z5:Z30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA51" s="39">
         <f>COUNTIF(AA5:AA30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AB51" s="39">
         <f>COUNTIF(AB5:AB30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC51" s="39">
         <f>COUNTIF(AC5:AC30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD51" s="39">
         <f>COUNTIF(AD5:AD30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE51" s="39">
         <f>COUNTIF(AE5:AE30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF51" s="39">
         <f>COUNTIF(AF5:AF30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG51" s="39">
         <f>COUNTIF(AG5:AG30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AH51" s="39">
         <f>COUNTIF(AH5:AH30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI51" s="39">
         <f>COUNTIF(AI5:AI30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ51" s="39">
         <f>COUNTIF(AJ5:AJ30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK51" s="39">
         <f>COUNTIF(AK5:AK30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL51" s="39">
         <f>COUNTIF(AL5:AL30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM51" s="39">
         <f>COUNTIF(AM5:AM30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AN51" s="39">
         <f>COUNTIF(AN5:AN30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO51" s="39">
         <f>COUNTIF(AO5:AO30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AP51" s="39">
         <f>COUNTIF(AP5:AP30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ51" s="39">
         <f>COUNTIF(AQ5:AQ30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AR51" s="39">
         <f>COUNTIF(AR5:AR30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS51" s="39">
         <f>COUNTIF(AS5:AS30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT51" s="39">
         <f>COUNTIF(AT5:AT30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU51" s="39">
         <f>COUNTIF(AU5:AU30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AV51" s="39">
         <f>COUNTIF(AV5:AV30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AW51" s="39">
         <f>COUNTIF(AW5:AW30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AX51" s="39">
         <f>COUNTIF(AX5:AX30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AY51" s="39">
         <f>COUNTIF(AY5:AY30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AZ51" s="39">
         <f>COUNTIF(AZ5:AZ30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BA51" s="39">
         <f>COUNTIF(BA5:BA30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB51" s="39">
         <f>COUNTIF(BB5:BB30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC51" s="39">
         <f>COUNTIF(BC5:BC30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD51" s="39">
         <f>COUNTIF(BD5:BD30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BE51" s="39">
         <f>COUNTIF(BE5:BE30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BF51" s="39">
         <f>COUNTIF(BF5:BF30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BG51" s="39">
         <f>COUNTIF(BG5:BG30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH51" s="39">
         <f>COUNTIF(BH5:BH30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BI51" s="39">
         <f>COUNTIF(BI5:BI30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BJ51" s="39">
         <f>COUNTIF(BJ5:BJ30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK51" s="39">
         <f>COUNTIF(BK5:BK30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL51" s="39">
         <f>COUNTIF(BL5:BL30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BM51" s="39">
         <f>COUNTIF(BM5:BM30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BN51" s="39">
         <f>COUNTIF(BN5:BN30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BO51" s="39">
         <f>COUNTIF(BO5:BO30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BP51" s="39">
         <f>COUNTIF(BP5:BP30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ51" s="39">
         <f>COUNTIF(BQ5:BQ30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BR51" s="39">
         <f>COUNTIF(BR5:BR30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BS51" s="39">
         <f>COUNTIF(BS5:BS30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BT51" s="39">
         <f>COUNTIF(BT5:BT30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BU51" s="39">
         <f>COUNTIF(BU5:BU30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BV51" s="39">
         <f>COUNTIF(BV5:BV30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BW51" s="39">
         <f>COUNTIF(BW5:BW30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX51" s="39">
         <f>COUNTIF(BX5:BX30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BY51" s="39">
         <f>COUNTIF(BY5:BY30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BZ51" s="39">
         <f>COUNTIF(BZ5:BZ30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CA51" s="39">
         <f>COUNTIF(CA5:CA30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CB51" s="39">
         <f>COUNTIF(CB5:CB30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CC51" s="39">
         <f>COUNTIF(CC5:CC30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CD51" s="39">
         <f>COUNTIF(CD5:CD30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE51" s="39">
         <f>COUNTIF(CE5:CE30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CF51" s="39">
         <f>COUNTIF(CF5:CF30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CG51" s="39">
         <f>COUNTIF(CG5:CG30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CH51" s="39">
         <f>COUNTIF(CH5:CH30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CI51" s="39">
         <f>COUNTIF(CI5:CI30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CJ51" s="39">
         <f>COUNTIF(CJ5:CJ30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK51" s="39">
         <f>COUNTIF(CK5:CK30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CL51" s="39">
         <f>COUNTIF(CL5:CL30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CM51" s="39">
         <f>COUNTIF(CM5:CM30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CN51" s="39">
         <f>COUNTIF(CN5:CN30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CO51" s="39">
         <f>COUNTIF(CO5:CO30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CP51" s="39">
         <f>COUNTIF(CP5:CP30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CQ51" s="39">
         <f>COUNTIF(CQ5:CQ30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CR51" s="39">
         <f>COUNTIF(CR5:CR30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CS51" s="39">
         <f>COUNTIF(CS5:CS30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CT51" s="39">
         <f>COUNTIF(CT5:CT30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CU51" s="39">
         <f>COUNTIF(CU5:CU30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CV51" s="39">
         <f>COUNTIF(CV5:CV30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CW51" s="39">
         <f>COUNTIF(CW5:CW30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CX51" s="39">
         <f>COUNTIF(CX5:CX30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CY51" s="39">
         <f>COUNTIF(CY5:CY30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CZ51" s="39">
         <f>COUNTIF(CZ5:CZ30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DA51" s="39">
         <f>COUNTIF(DA5:DA30,"X")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -14585,411 +14585,411 @@
       </c>
       <c r="D52" s="39">
         <f>COUNTIF(D5:D30,"~?")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E52" s="39">
         <f>COUNTIF(E5:E30,"~?")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F52" s="39">
         <f>COUNTIF(F5:F30,"~?")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G52" s="39">
         <f>COUNTIF(G5:G30,"~?")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H52" s="39">
         <f>COUNTIF(H5:H30,"~?")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I52" s="39">
         <f>COUNTIF(I5:I30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J52" s="39">
         <f>COUNTIF(J5:J30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K52" s="39">
         <f>COUNTIF(K5:K30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L52" s="39">
         <f>COUNTIF(L5:L30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M52" s="39">
         <f>COUNTIF(M5:M30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N52" s="39">
         <f>COUNTIF(N5:N30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O52" s="39">
         <f>COUNTIF(O5:O30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P52" s="39">
         <f>COUNTIF(P5:P30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q52" s="39">
         <f>COUNTIF(Q5:Q30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R52" s="39">
         <f>COUNTIF(R5:R30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S52" s="39">
         <f>COUNTIF(S5:S30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T52" s="39">
         <f>COUNTIF(T5:T30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U52" s="39">
         <f>COUNTIF(U5:U30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V52" s="39">
         <f>COUNTIF(V5:V30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W52" s="39">
         <f>COUNTIF(W5:W30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X52" s="39">
         <f>COUNTIF(X5:X30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y52" s="39">
         <f>COUNTIF(Y5:Y30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Z52" s="39">
         <f>COUNTIF(Z5:Z30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA52" s="39">
         <f>COUNTIF(AA5:AA30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AB52" s="39">
         <f>COUNTIF(AB5:AB30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC52" s="39">
         <f>COUNTIF(AC5:AC30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AD52" s="39">
         <f>COUNTIF(AD5:AD30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE52" s="39">
         <f>COUNTIF(AE5:AE30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF52" s="39">
         <f>COUNTIF(AF5:AF30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG52" s="39">
         <f>COUNTIF(AG5:AG30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AH52" s="39">
         <f>COUNTIF(AH5:AH30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI52" s="39">
         <f>COUNTIF(AI5:AI30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ52" s="39">
         <f>COUNTIF(AJ5:AJ30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK52" s="39">
         <f>COUNTIF(AK5:AK30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL52" s="39">
         <f>COUNTIF(AL5:AL30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM52" s="39">
         <f>COUNTIF(AM5:AM30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AN52" s="39">
         <f>COUNTIF(AN5:AN30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO52" s="39">
         <f>COUNTIF(AO5:AO30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AP52" s="39">
         <f>COUNTIF(AP5:AP30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ52" s="39">
         <f>COUNTIF(AQ5:AQ30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AR52" s="39">
         <f>COUNTIF(AR5:AR30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS52" s="39">
         <f>COUNTIF(AS5:AS30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT52" s="39">
         <f>COUNTIF(AT5:AT30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU52" s="39">
         <f>COUNTIF(AU5:AU30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AV52" s="39">
         <f>COUNTIF(AV5:AV30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AW52" s="39">
         <f>COUNTIF(AW5:AW30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AX52" s="39">
         <f>COUNTIF(AX5:AX30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AY52" s="39">
         <f>COUNTIF(AY5:AY30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AZ52" s="39">
         <f>COUNTIF(AZ5:AZ30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BA52" s="39">
         <f>COUNTIF(BA5:BA30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB52" s="39">
         <f>COUNTIF(BB5:BB30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC52" s="39">
         <f>COUNTIF(BC5:BC30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD52" s="39">
         <f>COUNTIF(BD5:BD30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BE52" s="39">
         <f>COUNTIF(BE5:BE30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BF52" s="39">
         <f>COUNTIF(BF5:BF30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BG52" s="39">
         <f>COUNTIF(BG5:BG30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH52" s="39">
         <f>COUNTIF(BH5:BH30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BI52" s="39">
         <f>COUNTIF(BI5:BI30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BJ52" s="39">
         <f>COUNTIF(BJ5:BJ30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BK52" s="39">
         <f>COUNTIF(BK5:BK30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL52" s="39">
         <f>COUNTIF(BL5:BL30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BM52" s="39">
         <f>COUNTIF(BM5:BM30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BN52" s="39">
         <f>COUNTIF(BN5:BN30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BO52" s="39">
         <f>COUNTIF(BO5:BO30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BP52" s="39">
         <f>COUNTIF(BP5:BP30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BQ52" s="39">
         <f>COUNTIF(BQ5:BQ30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BR52" s="39">
         <f>COUNTIF(BR5:BR30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BS52" s="39">
         <f>COUNTIF(BS5:BS30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BT52" s="39">
         <f>COUNTIF(BT5:BT30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BU52" s="39">
         <f>COUNTIF(BU5:BU30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BV52" s="39">
         <f>COUNTIF(BV5:BV30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BW52" s="39">
         <f>COUNTIF(BW5:BW30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BX52" s="39">
         <f>COUNTIF(BX5:BX30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BY52" s="39">
         <f>COUNTIF(BY5:BY30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BZ52" s="39">
         <f>COUNTIF(BZ5:BZ30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CA52" s="39">
         <f>COUNTIF(CA5:CA30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CB52" s="39">
         <f>COUNTIF(CB5:CB30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CC52" s="39">
         <f>COUNTIF(CC5:CC30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CD52" s="39">
         <f>COUNTIF(CD5:CD30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CE52" s="39">
         <f>COUNTIF(CE5:CE30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CF52" s="39">
         <f>COUNTIF(CF5:CF30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CG52" s="39">
         <f>COUNTIF(CG5:CG30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CH52" s="39">
         <f>COUNTIF(CH5:CH30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CI52" s="39">
         <f>COUNTIF(CI5:CI30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CJ52" s="39">
         <f>COUNTIF(CJ5:CJ30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CK52" s="39">
         <f>COUNTIF(CK5:CK30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CL52" s="39">
         <f>COUNTIF(CL5:CL30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CM52" s="39">
         <f>COUNTIF(CM5:CM30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CN52" s="39">
         <f>COUNTIF(CN5:CN30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CO52" s="39">
         <f>COUNTIF(CO5:CO30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CP52" s="39">
         <f>COUNTIF(CP5:CP30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CQ52" s="39">
         <f>COUNTIF(CQ5:CQ30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CR52" s="39">
         <f>COUNTIF(CR5:CR30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CS52" s="39">
         <f>COUNTIF(CS5:CS30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CT52" s="39">
         <f>COUNTIF(CT5:CT30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CU52" s="39">
         <f>COUNTIF(CU5:CU30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CV52" s="39">
         <f>COUNTIF(CV5:CV30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CW52" s="39">
         <f>COUNTIF(CW5:CW30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CX52" s="39">
         <f>COUNTIF(CX5:CX30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CY52" s="39">
         <f>COUNTIF(CY5:CY30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="CZ52" s="39">
         <f>COUNTIF(CZ5:CZ30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="DA52" s="39">
         <f>COUNTIF(DA5:DA30,"~?")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -15000,411 +15000,411 @@
       </c>
       <c r="D53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(D5:D30)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(E5:E30)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(F5:F30)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(G5:G30)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(H5:H30)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(I5:I30)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="J53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(J5:J30)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="K53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(K5:K30)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="L53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(L5:L30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="M53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(M5:M30)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="N53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(N5:N30)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="O53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(O5:O30)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(P5:P30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="Q53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(Q5:Q30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="R53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(R5:R30)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="S53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(S5:S30)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="T53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(T5:T30)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="U53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(U5:U30)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="V53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(V5:V30)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="W53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(W5:W30)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="X53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(X5:X30)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="Y53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(Y5:Y30)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="Z53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(Z5:Z30)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AA53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AA5:AA30)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AB53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AB5:AB30)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AC53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AC5:AC30)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AD53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AD5:AD30)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AE53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AE5:AE30)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AF53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AF5:AF30)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AG53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AG5:AG30)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AH53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AH5:AH30)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AI53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AI5:AI30)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AJ53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AJ5:AJ30)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="AK53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AK5:AK30)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="AL53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AL5:AL30)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="AM53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AM5:AM30)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="AN53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AN5:AN30)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="AO53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AO5:AO30)</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="AP53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AP5:AP30)</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="AQ53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AQ5:AQ30)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="AR53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AR5:AR30)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="AS53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AS5:AS30)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="AT53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AT5:AT30)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="AU53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AU5:AU30)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="AV53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AV5:AV30)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="AW53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AW5:AW30)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="AX53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AX5:AX30)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="AY53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AY5:AY30)</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="AZ53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(AZ5:AZ30)</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="BA53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BA5:BA30)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="BB53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BB5:BB30)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="BC53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BC5:BC30)</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="BD53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BD5:BD30)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="BE53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BE5:BE30)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="BF53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BF5:BF30)</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="BG53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BG5:BG30)</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="BH53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BH5:BH30)</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="BI53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BI5:BI30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BJ53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BJ5:BJ30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BK53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BK5:BK30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BL53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BL5:BL30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BM53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BM5:BM30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BN53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BN5:BN30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BO53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BO5:BO30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BP53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BP5:BP30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BQ53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BQ5:BQ30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BR53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BR5:BR30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BS53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BS5:BS30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BT53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BT5:BT30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BU53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BU5:BU30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BV53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BV5:BV30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BW53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BW5:BW30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BX53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BX5:BX30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BY53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BY5:BY30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="BZ53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(BZ5:BZ30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="CA53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CA5:CA30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="CB53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CB5:CB30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="CC53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CC5:CC30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="CD53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CD5:CD30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="CE53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CE5:CE30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="CF53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CF5:CF30)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="CG53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CG5:CG30)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="CH53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CH5:CH30)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="CI53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CI5:CI30)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="CJ53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CJ5:CJ30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CK53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CK5:CK30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CL53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CL5:CL30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CM53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CM5:CM30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CN53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CN5:CN30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CO53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CO5:CO30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CP53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CP5:CP30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CQ53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CQ5:CQ30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CR53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CR5:CR30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CS53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CS5:CS30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CT53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CT5:CT30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CU53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CU5:CU30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CV53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CV5:CV30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CW53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CW5:CW30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CX53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CX5:CX30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CY53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CY5:CY30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="CZ53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(CZ5:CZ30)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="DA53" s="39">
         <f>COUNTA($A$5:$A$30)-COUNTA(DA5:DA30)</f>
-        <v/>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -16218,7 +16218,7 @@
       </c>
       <c r="B29" s="24">
         <f>COUNTIF(C3:C27,"כן")</f>
-        <v/>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="B30" s="24">
         <f>COUNTIF(C3:C27,"לא")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="B31" s="24">
         <f>COUNTIF(C3:C28,"לא")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
